--- a/data/trending_integrated_20261008_13.xlsx
+++ b/data/trending_integrated_20261008_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>30990786390</v>
+        <v>31003942740</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11480</v>
+        <v>11360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.19%</t>
+          <t>'+14.98%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
         <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="H3" t="n">
         <v>37.45</v>
@@ -693,7 +693,7 @@
         <v>10030</v>
       </c>
       <c r="L3" t="n">
-        <v>11540</v>
+        <v>11570</v>
       </c>
       <c r="M3" t="n">
         <v>9850</v>
@@ -702,7 +702,7 @@
         <v>37.41</v>
       </c>
       <c r="O3" t="n">
-        <v>58753820855</v>
+        <v>60807349500</v>
       </c>
       <c r="P3" t="n">
         <v>19150</v>
@@ -711,10 +711,10 @@
         <v>3445</v>
       </c>
       <c r="R3" t="n">
-        <v>219000</v>
+        <v>197000</v>
       </c>
       <c r="S3" t="n">
-        <v>191000</v>
+        <v>452000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13600</v>
+        <v>13450</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.43%</t>
+          <t>'+12.18%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="H4" t="n">
         <v>4.43</v>
@@ -794,7 +794,7 @@
         <v>4.66</v>
       </c>
       <c r="O4" t="n">
-        <v>43753703965</v>
+        <v>44126140120</v>
       </c>
       <c r="P4" t="n">
         <v>14980</v>
@@ -803,23 +803,23 @@
         <v>6500</v>
       </c>
       <c r="R4" t="n">
-        <v>48000</v>
+        <v>-3000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>차세대 유리기판 핵심 부품 공동 개발 및 공급 시작. 삼성전기향 글라스 본더 공급 관련 호재 분석.</t>
+          <t>비아트론, 삼성전기와의 유리기판 본더 공동 개발 완료 및 본격 공급 소식에 따른 기대감 고조. 경쟁사 대비 높은 매출 및 영업이익, 배당금 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['유리기판', '글라스 본더', '공동 개발']</t>
+          <t>['유리기판', '글라스본더', '공동개발']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15600</v>
+        <v>6910</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.13%</t>
+          <t>'+6.97%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.15</v>
+        <v>-0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="F5" t="n">
-        <v>197</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>1182</v>
+        <v>184</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13790</v>
+        <v>6460</v>
       </c>
       <c r="K5" t="n">
-        <v>13410</v>
+        <v>6930</v>
       </c>
       <c r="L5" t="n">
-        <v>15800</v>
+        <v>8390</v>
       </c>
       <c r="M5" t="n">
-        <v>11600</v>
+        <v>6730</v>
       </c>
       <c r="N5" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="O5" t="n">
-        <v>104016559265</v>
+        <v>20550574320</v>
       </c>
       <c r="P5" t="n">
-        <v>28700</v>
+        <v>9680</v>
       </c>
       <c r="Q5" t="n">
-        <v>11600</v>
+        <v>371</v>
       </c>
       <c r="R5" t="n">
-        <v>17000</v>
+        <v>-27000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>누리호 발사 성공 및 핵심 부품 공급 사실 언급. 중복 상장 및 공매도 관련 불만 제기.</t>
+          <t>관리종목 해제 및 중견소속부 변경 호재에 대한 기대감 있으나, 주포 등장 및 거래량 부재, 매물대 걸림 등 불확실성 상존.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['누리호', '핵심 부품', '공매도']</t>
+          <t>['관리종목', '호재', '거래량']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6790</v>
+        <v>14700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.11%</t>
+          <t>'+6.60%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.31</v>
+        <v>-0.15</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>429</v>
       </c>
       <c r="F6" t="n">
-        <v>47</v>
+        <v>208</v>
       </c>
       <c r="G6" t="n">
-        <v>184</v>
+        <v>1256</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6460</v>
+        <v>13790</v>
       </c>
       <c r="K6" t="n">
-        <v>6930</v>
+        <v>13410</v>
       </c>
       <c r="L6" t="n">
-        <v>8390</v>
+        <v>15800</v>
       </c>
       <c r="M6" t="n">
-        <v>6730</v>
+        <v>11600</v>
       </c>
       <c r="N6" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="O6" t="n">
-        <v>20465732140</v>
+        <v>117202218425</v>
       </c>
       <c r="P6" t="n">
-        <v>9680</v>
+        <v>28700</v>
       </c>
       <c r="Q6" t="n">
-        <v>371</v>
+        <v>11600</v>
       </c>
       <c r="R6" t="n">
-        <v>-25000</v>
+        <v>26000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>관리종목 해제 및 중견소속부 변경 호재에 대한 기대감 있으나, 주포 등장 및 거래량 부재, 매물대 걸림 등 불확실성 상존.</t>
+          <t>덕산넵코어스, 중복 상장 및 공매도 허용으로 인한 주가 하락 및 투자자 손실 발생에 대한 강한 불만 표출. 사기 상장 의혹 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['관리종목', '호재', '거래량']</t>
+          <t>['중복상장', '공매도', '주가하락']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37950</v>
+        <v>13230</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.83%</t>
+          <t>'+5.25%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.08</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="F7" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G7" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>31.86</v>
+        <v>1.07</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>36200</v>
+        <v>12570</v>
       </c>
       <c r="K7" t="n">
-        <v>36250</v>
+        <v>12970</v>
       </c>
       <c r="L7" t="n">
-        <v>39850</v>
+        <v>14200</v>
       </c>
       <c r="M7" t="n">
-        <v>36000</v>
+        <v>12500</v>
       </c>
       <c r="N7" t="n">
-        <v>31.78</v>
+        <v>1.88</v>
       </c>
       <c r="O7" t="n">
-        <v>116645806025</v>
+        <v>82530608180</v>
       </c>
       <c r="P7" t="n">
-        <v>45000</v>
+        <v>22250</v>
       </c>
       <c r="Q7" t="n">
-        <v>15530</v>
+        <v>6000</v>
       </c>
       <c r="R7" t="n">
-        <v>199000</v>
+        <v>-501000</v>
       </c>
       <c r="S7" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>기관/외국인 매수세 유입 및 긍정적 추세 확인. 단, 실적 발표 후 차익실현 가능성 및 공매도 세력 언급.</t>
+          <t>HLB제약, 유증 물량 소화 및 추가 상승 기대감 표출. 바이오스텝과의 비교 및 1차 목표가 3만원 제시.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['기관', '외국인', '추세']</t>
+          <t>['유증물량', '추가상승', '목표가']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13140</v>
+        <v>37950</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.53%</t>
+          <t>'+4.83%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="F8" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G8" t="n">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="H8" t="n">
-        <v>1.07</v>
+        <v>31.86</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,60 +1147,60 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>12570</v>
+        <v>36200</v>
       </c>
       <c r="K8" t="n">
-        <v>12970</v>
+        <v>36250</v>
       </c>
       <c r="L8" t="n">
-        <v>14200</v>
+        <v>39850</v>
       </c>
       <c r="M8" t="n">
-        <v>12500</v>
+        <v>36000</v>
       </c>
       <c r="N8" t="n">
-        <v>1.88</v>
+        <v>31.78</v>
       </c>
       <c r="O8" t="n">
-        <v>81953167800</v>
+        <v>117820470500</v>
       </c>
       <c r="P8" t="n">
-        <v>22250</v>
+        <v>45000</v>
       </c>
       <c r="Q8" t="n">
-        <v>6000</v>
+        <v>15530</v>
       </c>
       <c r="R8" t="n">
-        <v>-324000</v>
+        <v>221000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>HLB 관련 기대감 및 비만치료제 개발 언급. 유증 물량 정리 후 상승 기대.</t>
+          <t>기관/외국인 매수세 유입 및 긍정적 추세 확인. 단, 실적 발표 후 차익실현 가능성 및 공매도 세력 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['HLB', '비만치료제', '유증 물량']</t>
+          <t>['기관', '외국인', '추세']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4460</v>
+        <v>4410</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.68%</t>
+          <t>'-0.45%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>1.19</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F9" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="H9" t="n">
         <v>4.46</v>
@@ -1254,7 +1254,7 @@
         <v>3.27</v>
       </c>
       <c r="O9" t="n">
-        <v>86721974234</v>
+        <v>87112212524</v>
       </c>
       <c r="P9" t="n">
         <v>5470</v>
@@ -1263,14 +1263,14 @@
         <v>2810</v>
       </c>
       <c r="R9" t="n">
-        <v>-469000</v>
+        <v>-471000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>전염병 관련 이슈로 인한 기대감 형성. WHO의 상황 파악 지연 및 확산세 둔화 가능성 언급.</t>
+          <t>러시아 관련 국제 정세 불안으로 인한 전염병 확산 우려에 따른 제약주 관심 증가. 일부 주가 급등 소식은 있으나 팩트 기반 분석은 부족.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['전염병', 'WHO']</t>
+          <t>['전염병', '제약주', '국제정세']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,184 +1299,184 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45650</v>
+        <v>8200</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.54%</t>
+          <t>'-0.61%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.73</v>
+        <v>-0.17</v>
       </c>
       <c r="E10" t="n">
-        <v>279</v>
+        <v>76</v>
       </c>
       <c r="F10" t="n">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>1067</v>
+        <v>237</v>
       </c>
       <c r="H10" t="n">
-        <v>13.39</v>
+        <v>26.38</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>45900</v>
+        <v>8250</v>
       </c>
       <c r="K10" t="n">
-        <v>45950</v>
+        <v>8190</v>
       </c>
       <c r="L10" t="n">
-        <v>46500</v>
+        <v>8320</v>
       </c>
       <c r="M10" t="n">
-        <v>45100</v>
+        <v>8090</v>
       </c>
       <c r="N10" t="n">
-        <v>14.12</v>
+        <v>26.55</v>
       </c>
       <c r="O10" t="n">
-        <v>29642089575</v>
+        <v>14736040415</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>8090</v>
       </c>
       <c r="R10" t="n">
-        <v>-12000</v>
+        <v>-51000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>111000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>리보세라닙 병용요법 허가 기대감 및 공매도 세력과의 갈등. 2026년 연말 30만 목표 제시.</t>
+          <t>LG디스플레이의 주가 하락 및 경영 부실에 대한 비판. 공매도와 천문학적 적자 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['리보세라닙', '공매도']</t>
+          <t>['주가 하락', '경영 부실', '적자']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8170</v>
+        <v>45600</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.97%</t>
+          <t>'-0.65%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.17</v>
+        <v>-0.73</v>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>285</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>161</v>
       </c>
       <c r="G11" t="n">
-        <v>231</v>
+        <v>1088</v>
       </c>
       <c r="H11" t="n">
-        <v>26.38</v>
+        <v>13.39</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8250</v>
+        <v>45900</v>
       </c>
       <c r="K11" t="n">
-        <v>8190</v>
+        <v>45950</v>
       </c>
       <c r="L11" t="n">
-        <v>8320</v>
+        <v>46500</v>
       </c>
       <c r="M11" t="n">
-        <v>8090</v>
+        <v>45100</v>
       </c>
       <c r="N11" t="n">
-        <v>26.55</v>
+        <v>14.12</v>
       </c>
       <c r="O11" t="n">
-        <v>14492017285</v>
+        <v>30024906775</v>
       </c>
       <c r="P11" t="n">
-        <v>17950</v>
+        <v>69200</v>
       </c>
       <c r="Q11" t="n">
-        <v>8090</v>
+        <v>24150</v>
       </c>
       <c r="R11" t="n">
-        <v>-6000</v>
+        <v>-66000</v>
       </c>
       <c r="S11" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>LG디스플레이의 주가 하락 및 경영 부실에 대한 비판. 공매도와 천문학적 적자 우려.</t>
+          <t>리보세라닙 병용요법 허가 기대감 및 공매도 세력과의 갈등. 2026년 연말 30만 목표 제시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가 하락', '경영 부실', '적자']</t>
+          <t>['리보세라닙', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1701000</v>
+        <v>1703000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.28%</t>
+          <t>'-1.16%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="G12" t="n">
-        <v>1432</v>
+        <v>1454</v>
       </c>
       <c r="H12" t="n">
         <v>49.59</v>
@@ -1530,7 +1530,7 @@
         <v>49.71</v>
       </c>
       <c r="O12" t="n">
-        <v>2912488042500</v>
+        <v>2999381065500</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1539,14 +1539,14 @@
         <v>403000</v>
       </c>
       <c r="R12" t="n">
-        <v>-25000</v>
+        <v>82000</v>
       </c>
       <c r="S12" t="n">
-        <v>-2000</v>
+        <v>-70000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>솔다임 상장 관련 의혹 제기 및 정부 비판. 주가 조작 의혹과 투자자 불만 표출.</t>
+          <t>SK하이닉스, 솔리다임 상장 관련 논란 및 국내 증시 전반의 부진에 대한 불만 표출. 정치적 요인과 주가 조작 의혹 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['솔다임', '주가 조작', '정부 비판']</t>
+          <t>['솔리다임', '주가조작', '국내증시']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="G13" t="n">
-        <v>1909</v>
+        <v>1973</v>
       </c>
       <c r="H13" t="n">
         <v>46.38</v>
@@ -1622,7 +1622,7 @@
         <v>46.37</v>
       </c>
       <c r="O13" t="n">
-        <v>2935769748000</v>
+        <v>3000053076000</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1631,14 +1631,14 @@
         <v>90200</v>
       </c>
       <c r="R13" t="n">
-        <v>36000</v>
+        <v>78000</v>
       </c>
       <c r="S13" t="n">
-        <v>-328000</v>
+        <v>-934000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대규모 영업이익에도 주가 부양 없다는 비관적 전망. 국장 현실과 삼성전자 주주 대상 사기 의혹 제기.</t>
+          <t>삼성전자 사상 최대 영업이익에도 불구하고 주가 부양 없는 증시 현실에 대한 불만 고조. 정치적 요인과 레버리지 관련 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 부양', '국장 현실']</t>
+          <t>['영업이익', '국내증시', '주가부양']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18900</v>
+        <v>18905</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.28%</t>
+          <t>'-3.25%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F14" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G14" t="n">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="H14" t="n">
         <v>27.68</v>
@@ -1714,7 +1714,7 @@
         <v>27.67</v>
       </c>
       <c r="O14" t="n">
-        <v>37874978905</v>
+        <v>38570803105</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
@@ -1723,10 +1723,10 @@
         <v>18440</v>
       </c>
       <c r="R14" t="n">
-        <v>-255000</v>
+        <v>-451000</v>
       </c>
       <c r="S14" t="n">
-        <v>-24000</v>
+        <v>-69000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16740</v>
+        <v>16720</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.46%</t>
+          <t>'-3.58%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="H15" t="n">
         <v>9.460000000000001</v>
@@ -1806,7 +1806,7 @@
         <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>35157785370</v>
+        <v>36071342795</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1815,14 +1815,14 @@
         <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>70000</v>
+        <v>-81000</v>
       </c>
       <c r="S15" t="n">
-        <v>-1000</v>
+        <v>-19000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>공매도 관련 게시글 다수. 주주들에게 대차 해지 중요성 호소.</t>
+          <t>대우건설, 공매도 및 주가 하락에 대한 불만과 함께 기관 매매에 대한 의혹 제기. 주주들에게 대차 해지의 중요성 강조.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도', '대차 해지']</t>
+          <t>['공매도', '주가하락', '기관매매']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>227500</v>
+        <v>229000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.60%</t>
+          <t>'-4.98%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.65</v>
       </c>
       <c r="E16" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F16" t="n">
         <v>70</v>
       </c>
       <c r="G16" t="n">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="H16" t="n">
         <v>3.47</v>
@@ -1898,7 +1898,7 @@
         <v>4.12</v>
       </c>
       <c r="O16" t="n">
-        <v>40552609750</v>
+        <v>40947001750</v>
       </c>
       <c r="P16" t="n">
         <v>1233000</v>
@@ -1907,14 +1907,14 @@
         <v>120000</v>
       </c>
       <c r="R16" t="n">
+        <v>6000</v>
+      </c>
+      <c r="S16" t="n">
         <v>5000</v>
       </c>
-      <c r="S16" t="n">
-        <v>2000</v>
-      </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>공매도 과열 종목 지정 및 연기금 매수 지속. 아일리아 관련 계약 공시 기대감.</t>
+          <t>삼천당제약, 아일리아 영업이익 전망 및 캐나다 세마 출시 기대감. 연기금 매수세와 공매도 금지 조치에 따른 상승 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공매도', '연기금', '아일리아']</t>
+          <t>['아일리아', '영업이익', '공매도금지']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28100</v>
+        <v>28200</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.70%</t>
+          <t>'-5.37%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.76</v>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G17" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H17" t="n">
         <v>10.02</v>
@@ -1990,7 +1990,7 @@
         <v>10.78</v>
       </c>
       <c r="O17" t="n">
-        <v>56764762825</v>
+        <v>57611606875</v>
       </c>
       <c r="P17" t="n">
         <v>75900</v>
@@ -1999,10 +1999,10 @@
         <v>15960</v>
       </c>
       <c r="R17" t="n">
-        <v>-380000</v>
+        <v>-560000</v>
       </c>
       <c r="S17" t="n">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2050,13 +2050,13 @@
         <v>-0.95</v>
       </c>
       <c r="E18" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F18" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G18" t="n">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H18" t="n">
         <v>3.97</v>
@@ -2082,7 +2082,7 @@
         <v>4.92</v>
       </c>
       <c r="O18" t="n">
-        <v>88505544690</v>
+        <v>89407816455</v>
       </c>
       <c r="P18" t="n">
         <v>31500</v>
@@ -2091,10 +2091,10 @@
         <v>1272</v>
       </c>
       <c r="R18" t="n">
-        <v>-168000</v>
+        <v>-426000</v>
       </c>
       <c r="S18" t="n">
-        <v>-15000</v>
+        <v>-60000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>75350</v>
+        <v>75200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.40%</t>
+          <t>'-6.58%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="F19" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G19" t="n">
-        <v>1144</v>
+        <v>1156</v>
       </c>
       <c r="H19" t="n">
         <v>22.49</v>
@@ -2168,13 +2168,13 @@
         <v>79600</v>
       </c>
       <c r="M19" t="n">
-        <v>75300</v>
+        <v>75200</v>
       </c>
       <c r="N19" t="n">
         <v>22.59</v>
       </c>
       <c r="O19" t="n">
-        <v>182640389750</v>
+        <v>186832443300</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2183,23 +2183,23 @@
         <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-360000</v>
+        <v>-579000</v>
       </c>
       <c r="S19" t="n">
-        <v>-54000</v>
+        <v>-91000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 가스 발전 사업 확정 소식에도 주가 하락. 공매도와 원전 사업 불확실성 언급.</t>
+          <t>두산에너빌리티, 해외 가스 발전 수주 기대감에도 불구하고 주가 하락에 대한 답답함 표출. 공매도 및 주가 하락 원인에 대한 의문 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['가스발전', '공매도', '원전']</t>
+          <t>['가스발전', '주가하락', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7310</v>
+        <v>7250</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.52%</t>
+          <t>'-7.29%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-2.03</v>
       </c>
       <c r="E20" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F20" t="n">
         <v>84</v>
       </c>
       <c r="G20" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="H20" t="n">
         <v>3.09</v>
@@ -2266,7 +2266,7 @@
         <v>5.12</v>
       </c>
       <c r="O20" t="n">
-        <v>81730900075</v>
+        <v>82154805565</v>
       </c>
       <c r="P20" t="n">
         <v>23500</v>
@@ -2275,7 +2275,7 @@
         <v>2890</v>
       </c>
       <c r="R20" t="n">
-        <v>-501000</v>
+        <v>-518000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4810</v>
+        <v>4815</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.68%</t>
+          <t>'-7.58%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2358,7 +2358,7 @@
         <v>4.72</v>
       </c>
       <c r="O21" t="n">
-        <v>65745428386</v>
+        <v>66193760326</v>
       </c>
       <c r="P21" t="n">
         <v>8100</v>
@@ -2367,7 +2367,7 @@
         <v>592</v>
       </c>
       <c r="R21" t="n">
-        <v>-152000</v>
+        <v>-237000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>53300</v>
+        <v>52700</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.26%</t>
+          <t>'-9.29%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.02</v>
       </c>
       <c r="E22" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F22" t="n">
         <v>147</v>
       </c>
       <c r="G22" t="n">
-        <v>567</v>
+        <v>595</v>
       </c>
       <c r="H22" t="n">
         <v>1.32</v>
@@ -2444,13 +2444,13 @@
         <v>63800</v>
       </c>
       <c r="M22" t="n">
-        <v>52900</v>
+        <v>52500</v>
       </c>
       <c r="N22" t="n">
         <v>1.3</v>
       </c>
       <c r="O22" t="n">
-        <v>51976083650</v>
+        <v>52613399450</v>
       </c>
       <c r="P22" t="n">
         <v>63800</v>
@@ -2459,14 +2459,14 @@
         <v>25600</v>
       </c>
       <c r="R22" t="n">
-        <v>-170000</v>
+        <v>-173000</v>
       </c>
       <c r="S22" t="n">
-        <v>-21000</v>
+        <v>-30000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>비만약 기술 수출 관련 불확실성 속 급락. 주가 조작 및 공매도 의혹 제기.</t>
+          <t>한미사이언스, 국내 시장 석권 준비 및 미국 비만주 급등에 따른 기대감 표출. 그러나 식약처 승인에도 불구하고 급락한 주가와 공매도, 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['비만약', '기술 수출', '공매도']</t>
+          <t>['비만치료제', '공매도', '주가조작']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2495,79 +2495,79 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9820</v>
+        <v>15000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-10.81%</t>
+          <t>'-10.23%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.03</v>
+        <v>-1.44</v>
       </c>
       <c r="E23" t="n">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="F23" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="G23" t="n">
-        <v>350</v>
+        <v>184</v>
       </c>
       <c r="H23" t="n">
-        <v>5.04</v>
+        <v>0.93</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>11010</v>
+        <v>16710</v>
       </c>
       <c r="K23" t="n">
-        <v>10110</v>
+        <v>16460</v>
       </c>
       <c r="L23" t="n">
-        <v>10130</v>
+        <v>17180</v>
       </c>
       <c r="M23" t="n">
-        <v>9750</v>
+        <v>14820</v>
       </c>
       <c r="N23" t="n">
-        <v>5.01</v>
+        <v>2.37</v>
       </c>
       <c r="O23" t="n">
-        <v>6872879730</v>
+        <v>33941054950</v>
       </c>
       <c r="P23" t="n">
-        <v>15900</v>
+        <v>17590</v>
       </c>
       <c r="Q23" t="n">
-        <v>6310</v>
+        <v>6320</v>
       </c>
       <c r="R23" t="n">
-        <v>-302000</v>
+        <v>12000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>미국 항생제 관련주 폭등 속 신풍제약 주가 부진. 바이러스 대장주로서의 기대감과 함께 주가 장난질에 대한 불만 표출.</t>
+          <t>KDB생명 해킹 방어 성공 및 AI 사이버보안 협의체 선정 뉴스. SKT와의 협력 기반 역대 고점 돌파 기대.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['항생제 관련주', '주가 부진', '바이러스 대장주']</t>
+          <t>['양자보안', 'AI', '사이버보안']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2575,91 +2575,91 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14890</v>
+        <v>9830</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.89%</t>
+          <t>'-10.72%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-1.44</v>
+        <v>0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="F24" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="G24" t="n">
-        <v>183</v>
+        <v>352</v>
       </c>
       <c r="H24" t="n">
-        <v>0.93</v>
+        <v>5.04</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>16710</v>
+        <v>11010</v>
       </c>
       <c r="K24" t="n">
-        <v>16460</v>
+        <v>10110</v>
       </c>
       <c r="L24" t="n">
-        <v>17180</v>
+        <v>10130</v>
       </c>
       <c r="M24" t="n">
-        <v>14820</v>
+        <v>9750</v>
       </c>
       <c r="N24" t="n">
-        <v>2.37</v>
+        <v>5.01</v>
       </c>
       <c r="O24" t="n">
-        <v>33709282670</v>
+        <v>6924651815</v>
       </c>
       <c r="P24" t="n">
-        <v>17590</v>
+        <v>15900</v>
       </c>
       <c r="Q24" t="n">
-        <v>6320</v>
+        <v>6310</v>
       </c>
       <c r="R24" t="n">
-        <v>20000</v>
+        <v>-325000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>KDB생명 해킹 방어 성공 및 AI 사이버보안 협의체 선정 뉴스. SKT와의 협력 기반 역대 고점 돌파 기대.</t>
+          <t>신풍제약 주가 급등 해외 사례 언급, 에볼라 관련 기대감 있으나 매도 의견 및 개인 투자자들의 혼조세 관찰됨.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['양자보안', 'AI', '사이버보안']</t>
+          <t>['신풍제약', '항생제', '에볼라']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>019170</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261008_13.xlsx
+++ b/data/trending_integrated_20261008_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31003942740</v>
+        <v>31019515820</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11360</v>
+        <v>11530</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.98%</t>
+          <t>'+16.70%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="H3" t="n">
         <v>37.45</v>
@@ -702,7 +702,7 @@
         <v>37.41</v>
       </c>
       <c r="O3" t="n">
-        <v>60807349500</v>
+        <v>61999507530</v>
       </c>
       <c r="P3" t="n">
         <v>19150</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13450</v>
+        <v>13310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.18%</t>
+          <t>'+11.01%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H4" t="n">
         <v>4.43</v>
@@ -794,7 +794,7 @@
         <v>4.66</v>
       </c>
       <c r="O4" t="n">
-        <v>44126140120</v>
+        <v>45023097195</v>
       </c>
       <c r="P4" t="n">
         <v>14980</v>
@@ -843,18 +843,18 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6910</v>
+        <v>6770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.97%</t>
+          <t>'+4.80%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.31</v>
       </c>
       <c r="E5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F5" t="n">
         <v>48</v>
@@ -886,7 +886,7 @@
         <v>0.31</v>
       </c>
       <c r="O5" t="n">
-        <v>20550574320</v>
+        <v>20675357730</v>
       </c>
       <c r="P5" t="n">
         <v>9680</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14700</v>
+        <v>14450</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.60%</t>
+          <t>'+4.79%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.15</v>
       </c>
       <c r="E6" t="n">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="F6" t="n">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="G6" t="n">
-        <v>1256</v>
+        <v>1327</v>
       </c>
       <c r="H6" t="n">
         <v>0.09</v>
@@ -978,7 +978,7 @@
         <v>0.24</v>
       </c>
       <c r="O6" t="n">
-        <v>117202218425</v>
+        <v>130769852350</v>
       </c>
       <c r="P6" t="n">
         <v>28700</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>덕산넵코어스, 중복 상장 및 공매도 허용으로 인한 주가 하락 및 투자자 손실 발생에 대한 강한 불만 표출. 사기 상장 의혹 제기.</t>
+          <t>덕산넵코어스의 사기 상장 의혹 제기 및 국민권익위, 금감원 신고 언급. 주가 하락에 대한 강한 불만.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['중복상장', '공매도', '주가하락']</t>
+          <t>['사기상장', '국민권익위', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13230</v>
+        <v>37900</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.25%</t>
+          <t>'+4.70%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="F7" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="H7" t="n">
-        <v>1.07</v>
+        <v>31.86</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>12570</v>
+        <v>36200</v>
       </c>
       <c r="K7" t="n">
-        <v>12970</v>
+        <v>36250</v>
       </c>
       <c r="L7" t="n">
-        <v>14200</v>
+        <v>39850</v>
       </c>
       <c r="M7" t="n">
-        <v>12500</v>
+        <v>36000</v>
       </c>
       <c r="N7" t="n">
-        <v>1.88</v>
+        <v>31.78</v>
       </c>
       <c r="O7" t="n">
-        <v>82530608180</v>
+        <v>119170391800</v>
       </c>
       <c r="P7" t="n">
-        <v>22250</v>
+        <v>45000</v>
       </c>
       <c r="Q7" t="n">
-        <v>6000</v>
+        <v>15530</v>
       </c>
       <c r="R7" t="n">
-        <v>-501000</v>
+        <v>221000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>HLB제약, 유증 물량 소화 및 추가 상승 기대감 표출. 바이오스텝과의 비교 및 1차 목표가 3만원 제시.</t>
+          <t>기관/외국인 매수세 유입 및 긍정적 추세 확인. 단, 실적 발표 후 차익실현 가능성 및 공매도 세력 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유증물량', '추가상승', '목표가']</t>
+          <t>['기관', '외국인', '추세']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37950</v>
+        <v>13150</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.83%</t>
+          <t>'+4.61%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.08</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="F8" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="G8" t="n">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="H8" t="n">
-        <v>31.86</v>
+        <v>1.07</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,60 +1147,60 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>36200</v>
+        <v>12570</v>
       </c>
       <c r="K8" t="n">
-        <v>36250</v>
+        <v>12970</v>
       </c>
       <c r="L8" t="n">
-        <v>39850</v>
+        <v>14200</v>
       </c>
       <c r="M8" t="n">
-        <v>36000</v>
+        <v>12500</v>
       </c>
       <c r="N8" t="n">
-        <v>31.78</v>
+        <v>1.88</v>
       </c>
       <c r="O8" t="n">
-        <v>117820470500</v>
+        <v>83164826725</v>
       </c>
       <c r="P8" t="n">
-        <v>45000</v>
+        <v>22250</v>
       </c>
       <c r="Q8" t="n">
-        <v>15530</v>
+        <v>6000</v>
       </c>
       <c r="R8" t="n">
-        <v>221000</v>
+        <v>-501000</v>
       </c>
       <c r="S8" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>기관/외국인 매수세 유입 및 긍정적 추세 확인. 단, 실적 발표 후 차익실현 가능성 및 공매도 세력 언급.</t>
+          <t>HLB제약의 유증 물량 정리 및 1차 목표가 3만원 제시. 바이오스텝과의 비교 및 HLB 승인 시 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['기관', '외국인', '추세']</t>
+          <t>['유증물량', '목표가', '바이오']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4410</v>
+        <v>4415</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.45%</t>
+          <t>'-0.34%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>1.19</v>
       </c>
       <c r="E9" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F9" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G9" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H9" t="n">
         <v>4.46</v>
@@ -1254,7 +1254,7 @@
         <v>3.27</v>
       </c>
       <c r="O9" t="n">
-        <v>87112212524</v>
+        <v>87400570969</v>
       </c>
       <c r="P9" t="n">
         <v>5470</v>
@@ -1314,13 +1314,13 @@
         <v>-0.17</v>
       </c>
       <c r="E10" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F10" t="n">
         <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="H10" t="n">
         <v>26.38</v>
@@ -1346,7 +1346,7 @@
         <v>26.55</v>
       </c>
       <c r="O10" t="n">
-        <v>14736040415</v>
+        <v>15122677110</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1406,13 +1406,13 @@
         <v>-0.73</v>
       </c>
       <c r="E11" t="n">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="F11" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G11" t="n">
-        <v>1088</v>
+        <v>1114</v>
       </c>
       <c r="H11" t="n">
         <v>13.39</v>
@@ -1438,7 +1438,7 @@
         <v>14.12</v>
       </c>
       <c r="O11" t="n">
-        <v>30024906775</v>
+        <v>30688459450</v>
       </c>
       <c r="P11" t="n">
         <v>69200</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>리보세라닙 병용요법 허가 기대감 및 공매도 세력과의 갈등. 2026년 연말 30만 목표 제시.</t>
+          <t>HLB의 리보세라닙 병용요법 허가 기대감 및 2026년 연말 30만 목표 제시. 공매도 발악 및 숏스퀴즈 현실화 가능성 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['리보세라닙', '공매도']</t>
+          <t>['리보세라닙', '공매도', '숏스퀴즈']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1703000</v>
+        <v>1704000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.16%</t>
+          <t>'-1.10%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="G12" t="n">
-        <v>1454</v>
+        <v>1506</v>
       </c>
       <c r="H12" t="n">
         <v>49.59</v>
@@ -1530,7 +1530,7 @@
         <v>49.71</v>
       </c>
       <c r="O12" t="n">
-        <v>2999381065500</v>
+        <v>3067507399500</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>SK하이닉스, 솔리다임 상장 관련 논란 및 국내 증시 전반의 부진에 대한 불만 표출. 정치적 요인과 주가 조작 의혹 언급.</t>
+          <t>정치적 요인으로 인한 증시 하락 및 '이재명 정부'에 대한 불만 토로. 솔리다임 상장 이슈와 주가 하락에 대한 불만.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['솔리다임', '주가조작', '국내증시']</t>
+          <t>['솔리다임', '국장', '정치']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G13" t="n">
-        <v>1973</v>
+        <v>2017</v>
       </c>
       <c r="H13" t="n">
         <v>46.38</v>
@@ -1622,7 +1622,7 @@
         <v>46.37</v>
       </c>
       <c r="O13" t="n">
-        <v>3000053076000</v>
+        <v>3078241747750</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>삼성전자 사상 최대 영업이익에도 불구하고 주가 부양 없는 증시 현실에 대한 불만 고조. 정치적 요인과 레버리지 관련 언급.</t>
+          <t>정치적 요인으로 인한 증시 하락 및 '이재명 정부'에 대한 불만 토로. 낮은 주가와 실적 간의 괴리에 대한 불만.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['영업이익', '국내증시', '주가부양']</t>
+          <t>['레버리지', '국장', '실적']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18905</v>
+        <v>18890</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.25%</t>
+          <t>'-3.33%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F14" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G14" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H14" t="n">
         <v>27.68</v>
@@ -1708,13 +1708,13 @@
         <v>19500</v>
       </c>
       <c r="M14" t="n">
-        <v>18890</v>
+        <v>18880</v>
       </c>
       <c r="N14" t="n">
         <v>27.67</v>
       </c>
       <c r="O14" t="n">
-        <v>38570803105</v>
+        <v>39289490245</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16720</v>
+        <v>16710</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.58%</t>
+          <t>'-3.63%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F15" t="n">
         <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>491</v>
+        <v>544</v>
       </c>
       <c r="H15" t="n">
         <v>9.460000000000001</v>
@@ -1800,13 +1800,13 @@
         <v>17220</v>
       </c>
       <c r="M15" t="n">
-        <v>16710</v>
+        <v>16700</v>
       </c>
       <c r="N15" t="n">
         <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>36071342795</v>
+        <v>37238195625</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대우건설, 공매도 및 주가 하락에 대한 불만과 함께 기관 매매에 대한 의혹 제기. 주주들에게 대차 해지의 중요성 강조.</t>
+          <t>대우건설 주주들에게 공매도와 대차 해지의 중요성을 호소. 주가 조작 및 공매도에 대한 불만.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도', '주가하락', '기관매매']</t>
+          <t>['공매도', '대차해지', '주가조작']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>229000</v>
+        <v>230000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.98%</t>
+          <t>'-4.56%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.65</v>
       </c>
       <c r="E16" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" t="n">
-        <v>730</v>
+        <v>749</v>
       </c>
       <c r="H16" t="n">
         <v>3.47</v>
@@ -1898,7 +1898,7 @@
         <v>4.12</v>
       </c>
       <c r="O16" t="n">
-        <v>40947001750</v>
+        <v>41364793750</v>
       </c>
       <c r="P16" t="n">
         <v>1233000</v>
@@ -1958,13 +1958,13 @@
         <v>-0.76</v>
       </c>
       <c r="E17" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F17" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G17" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H17" t="n">
         <v>10.02</v>
@@ -1990,7 +1990,7 @@
         <v>10.78</v>
       </c>
       <c r="O17" t="n">
-        <v>57611606875</v>
+        <v>58451895025</v>
       </c>
       <c r="P17" t="n">
         <v>75900</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16830</v>
+        <v>16880</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.19%</t>
+          <t>'-5.91%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.95</v>
       </c>
       <c r="E18" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F18" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G18" t="n">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="H18" t="n">
         <v>3.97</v>
@@ -2082,7 +2082,7 @@
         <v>4.92</v>
       </c>
       <c r="O18" t="n">
-        <v>89407816455</v>
+        <v>90962801640</v>
       </c>
       <c r="P18" t="n">
         <v>31500</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 하락 영향 언급. 외인, 기관 쌍매도 및 프로그램 매매 불안감 표출.</t>
+          <t>미국 광통신 주가 하락에 따른 대한광통신의 우려. 외인 및 기관 쌍매도, 프로그램 매매 불안감 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신', '외인 매도', '프로그램 매매']</t>
+          <t>['광통신', '수급', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>75200</v>
+        <v>75400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.58%</t>
+          <t>'-6.34%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="F19" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="G19" t="n">
-        <v>1156</v>
+        <v>1192</v>
       </c>
       <c r="H19" t="n">
         <v>22.49</v>
@@ -2174,7 +2174,7 @@
         <v>22.59</v>
       </c>
       <c r="O19" t="n">
-        <v>186832443300</v>
+        <v>191974582950</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7250</v>
+        <v>7210</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.29%</t>
+          <t>'-7.80%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-2.03</v>
       </c>
       <c r="E20" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F20" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G20" t="n">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="H20" t="n">
         <v>3.09</v>
@@ -2266,7 +2266,7 @@
         <v>5.12</v>
       </c>
       <c r="O20" t="n">
-        <v>82154805565</v>
+        <v>82619437510</v>
       </c>
       <c r="P20" t="n">
         <v>23500</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>본PF 및 대주단 구성 진행 상황 언급. 급등 챠트와 물량 간수 관련 내용 포함.</t>
+          <t>삼표시멘트의 본PF 구성 및 대주단 구성 관련 정보 언급. 주가 흐름에 대한 분석 및 주의 촉구.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['본PF', '대주단', '물량 간수']</t>
+          <t>['본PF', '대주단', '주포']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4815</v>
+        <v>4790</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.58%</t>
+          <t>'-8.06%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F21" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G21" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H21" t="n">
         <v>4.65</v>
@@ -2358,7 +2358,7 @@
         <v>4.72</v>
       </c>
       <c r="O21" t="n">
-        <v>66193760326</v>
+        <v>66756965598</v>
       </c>
       <c r="P21" t="n">
         <v>8100</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52700</v>
+        <v>52600</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.29%</t>
+          <t>'-9.47%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.02</v>
       </c>
       <c r="E22" t="n">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="F22" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G22" t="n">
-        <v>595</v>
+        <v>615</v>
       </c>
       <c r="H22" t="n">
         <v>1.32</v>
@@ -2450,7 +2450,7 @@
         <v>1.3</v>
       </c>
       <c r="O22" t="n">
-        <v>52613399450</v>
+        <v>53239790050</v>
       </c>
       <c r="P22" t="n">
         <v>63800</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>한미사이언스, 국내 시장 석권 준비 및 미국 비만주 급등에 따른 기대감 표출. 그러나 식약처 승인에도 불구하고 급락한 주가와 공매도, 주가 조작 의혹 제기.</t>
+          <t>한미사이언스의 미국 비만주 급등과 비교하며 국내 시장 석권 준비 완료 언급. 승인 및 기술수출에도 급락하는 주가에 대한 불만.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['비만치료제', '공매도', '주가조작']</t>
+          <t>['비만치료제', '기술수출', '공매도']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15000</v>
+        <v>15050</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-10.23%</t>
+          <t>'-9.93%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-1.44</v>
       </c>
       <c r="E23" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F23" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G23" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="H23" t="n">
         <v>0.93</v>
@@ -2542,7 +2542,7 @@
         <v>2.37</v>
       </c>
       <c r="O23" t="n">
-        <v>33941054950</v>
+        <v>34161131580</v>
       </c>
       <c r="P23" t="n">
         <v>17590</v>
@@ -2602,13 +2602,13 @@
         <v>0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F24" t="n">
         <v>63</v>
       </c>
       <c r="G24" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="H24" t="n">
         <v>5.04</v>
@@ -2634,7 +2634,7 @@
         <v>5.01</v>
       </c>
       <c r="O24" t="n">
-        <v>6924651815</v>
+        <v>6970537525</v>
       </c>
       <c r="P24" t="n">
         <v>15900</v>

--- a/data/trending_integrated_20261008_13.xlsx
+++ b/data/trending_integrated_20261008_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F2" t="n">
         <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31019515820</v>
+        <v>31048062260</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11530</v>
+        <v>11490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.70%</t>
+          <t>'+16.30%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="H3" t="n">
         <v>37.45</v>
@@ -702,7 +702,7 @@
         <v>37.41</v>
       </c>
       <c r="O3" t="n">
-        <v>61999507530</v>
+        <v>63011352070</v>
       </c>
       <c r="P3" t="n">
         <v>19150</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13310</v>
+        <v>13250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.01%</t>
+          <t>'+10.51%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F4" t="n">
         <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H4" t="n">
         <v>4.43</v>
@@ -794,7 +794,7 @@
         <v>4.66</v>
       </c>
       <c r="O4" t="n">
-        <v>45023097195</v>
+        <v>45620874775</v>
       </c>
       <c r="P4" t="n">
         <v>14980</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>비아트론, 삼성전기와의 유리기판 본더 공동 개발 완료 및 본격 공급 소식에 따른 기대감 고조. 경쟁사 대비 높은 매출 및 영업이익, 배당금 언급.</t>
+          <t>유리기판 공정용 글라스본더 개발 완료. 삼성전기 공동 개발, 동종 업체 대비 월등한 실적 및 낮은 시총 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['유리기판', '글라스본더', '공동개발']</t>
+          <t>['글라스본더', '유리기판', '공동개발']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6770</v>
+        <v>14630</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.80%</t>
+          <t>'+6.09%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.31</v>
+        <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>83</v>
+        <v>476</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>225</v>
       </c>
       <c r="G5" t="n">
-        <v>184</v>
+        <v>1384</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6460</v>
+        <v>13790</v>
       </c>
       <c r="K5" t="n">
-        <v>6930</v>
+        <v>13410</v>
       </c>
       <c r="L5" t="n">
-        <v>8390</v>
+        <v>15800</v>
       </c>
       <c r="M5" t="n">
-        <v>6730</v>
+        <v>11600</v>
       </c>
       <c r="N5" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="O5" t="n">
-        <v>20675357730</v>
+        <v>137092875750</v>
       </c>
       <c r="P5" t="n">
-        <v>9680</v>
+        <v>28700</v>
       </c>
       <c r="Q5" t="n">
-        <v>371</v>
+        <v>11600</v>
       </c>
       <c r="R5" t="n">
-        <v>-27000</v>
+        <v>26000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>관리종목 해제 및 중견소속부 변경 호재에 대한 기대감 있으나, 주포 등장 및 거래량 부재, 매물대 걸림 등 불확실성 상존.</t>
+          <t>중복 상장 금지 예외 허용 및 무차별 공매도에 대한 강한 불만. 사기 상장 의혹 제기와 함께 주가 하락에 대한 우려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['관리종목', '호재', '거래량']</t>
+          <t>['중복상장', '공매도', '사기상장']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14450</v>
+        <v>38250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.79%</t>
+          <t>'+5.66%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.15</v>
+        <v>0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>451</v>
+        <v>80</v>
       </c>
       <c r="F6" t="n">
-        <v>218</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
-        <v>1327</v>
+        <v>183</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09</v>
+        <v>31.86</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13790</v>
+        <v>36200</v>
       </c>
       <c r="K6" t="n">
-        <v>13410</v>
+        <v>36250</v>
       </c>
       <c r="L6" t="n">
-        <v>15800</v>
+        <v>39850</v>
       </c>
       <c r="M6" t="n">
-        <v>11600</v>
+        <v>36000</v>
       </c>
       <c r="N6" t="n">
-        <v>0.24</v>
+        <v>31.78</v>
       </c>
       <c r="O6" t="n">
-        <v>130769852350</v>
+        <v>120644692500</v>
       </c>
       <c r="P6" t="n">
-        <v>28700</v>
+        <v>45000</v>
       </c>
       <c r="Q6" t="n">
-        <v>11600</v>
+        <v>15530</v>
       </c>
       <c r="R6" t="n">
-        <v>26000</v>
+        <v>221000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>덕산넵코어스의 사기 상장 의혹 제기 및 국민권익위, 금감원 신고 언급. 주가 하락에 대한 강한 불만.</t>
+          <t>하락장 속 고영 주가 선방. JP모건의 미친듯한 매수세 확인, 추세 긍정적 평가. 외국인 순매수세 관찰.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['사기상장', '국민권익위', '공매도']</t>
+          <t>['외국인', '매수세', '추세']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37900</v>
+        <v>6750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.70%</t>
+          <t>'+4.49%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.08</v>
+        <v>-0.31</v>
       </c>
       <c r="E7" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="H7" t="n">
-        <v>31.86</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>36200</v>
+        <v>6460</v>
       </c>
       <c r="K7" t="n">
-        <v>36250</v>
+        <v>6930</v>
       </c>
       <c r="L7" t="n">
-        <v>39850</v>
+        <v>8390</v>
       </c>
       <c r="M7" t="n">
-        <v>36000</v>
+        <v>6730</v>
       </c>
       <c r="N7" t="n">
-        <v>31.78</v>
+        <v>0.31</v>
       </c>
       <c r="O7" t="n">
-        <v>119170391800</v>
+        <v>20761354465</v>
       </c>
       <c r="P7" t="n">
-        <v>45000</v>
+        <v>9680</v>
       </c>
       <c r="Q7" t="n">
-        <v>15530</v>
+        <v>371</v>
       </c>
       <c r="R7" t="n">
-        <v>221000</v>
+        <v>-27000</v>
       </c>
       <c r="S7" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>기관/외국인 매수세 유입 및 긍정적 추세 확인. 단, 실적 발표 후 차익실현 가능성 및 공매도 세력 언급.</t>
+          <t>관리종목 해제 및 거래 정상화 호재. 새 주인 확정 기대감 속 주포 움직임 주시, 재료 소멸 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['기관', '외국인', '추세']</t>
+          <t>['관리종목', '거래정상화', '주포']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13150</v>
+        <v>13110</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.61%</t>
+          <t>'+4.30%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.8100000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F8" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G8" t="n">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="H8" t="n">
         <v>1.07</v>
@@ -1162,7 +1162,7 @@
         <v>1.88</v>
       </c>
       <c r="O8" t="n">
-        <v>83164826725</v>
+        <v>83453873915</v>
       </c>
       <c r="P8" t="n">
         <v>22250</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>HLB제약의 유증 물량 정리 및 1차 목표가 3만원 제시. 바이오스텝과의 비교 및 HLB 승인 시 기대감.</t>
+          <t>유증 물량 정리 및 1차 목표가 3만원 제시. 바이오스텝과의 연관성을 언급하며 상승 가능성에 대한 기대감 표현.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['유증물량', '목표가', '바이오']</t>
+          <t>['유증', '목표주가', '바이오스텝']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4415</v>
+        <v>4430</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.34%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>1.19</v>
       </c>
       <c r="E9" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F9" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G9" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H9" t="n">
         <v>4.46</v>
@@ -1254,7 +1254,7 @@
         <v>3.27</v>
       </c>
       <c r="O9" t="n">
-        <v>87400570969</v>
+        <v>88015825743</v>
       </c>
       <c r="P9" t="n">
         <v>5470</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8200</v>
+        <v>8230</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.61%</t>
+          <t>'-0.24%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.17</v>
       </c>
       <c r="E10" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="H10" t="n">
         <v>26.38</v>
@@ -1346,7 +1346,7 @@
         <v>26.55</v>
       </c>
       <c r="O10" t="n">
-        <v>15122677110</v>
+        <v>15517760345</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>LG디스플레이의 주가 하락 및 경영 부실에 대한 비판. 공매도와 천문학적 적자 우려.</t>
+          <t>과도한 투자 대비 낮은 시가총액에 대한 비판과 경영 방식에 대한 의문. 공매도와 유증에 대한 부정적 인식.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주가 하락', '경영 부실', '적자']</t>
+          <t>['시가총액', '공매도', '유증']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1406,13 +1406,13 @@
         <v>-0.73</v>
       </c>
       <c r="E11" t="n">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="F11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G11" t="n">
-        <v>1114</v>
+        <v>1133</v>
       </c>
       <c r="H11" t="n">
         <v>13.39</v>
@@ -1438,7 +1438,7 @@
         <v>14.12</v>
       </c>
       <c r="O11" t="n">
-        <v>30688459450</v>
+        <v>30936480250</v>
       </c>
       <c r="P11" t="n">
         <v>69200</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1704000</v>
+        <v>1710000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.10%</t>
+          <t>'-0.75%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="G12" t="n">
-        <v>1506</v>
+        <v>1525</v>
       </c>
       <c r="H12" t="n">
         <v>49.59</v>
@@ -1530,7 +1530,7 @@
         <v>49.71</v>
       </c>
       <c r="O12" t="n">
-        <v>3067507399500</v>
+        <v>3147694431500</v>
       </c>
       <c r="P12" t="n">
         <v>2987000</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 요인으로 인한 증시 하락 및 '이재명 정부'에 대한 불만 토로. 솔리다임 상장 이슈와 주가 하락에 대한 불만.</t>
+          <t>솔리다임 상장 및 중복 상장에 대한 비판과 정부 정책에 대한 불만. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['솔리다임', '국장', '정치']</t>
+          <t>['솔리다임', '중복상장', '주가조작']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>264250</v>
+        <v>264750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.58%</t>
+          <t>'-1.40%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G13" t="n">
-        <v>2017</v>
+        <v>2058</v>
       </c>
       <c r="H13" t="n">
         <v>46.38</v>
@@ -1622,7 +1622,7 @@
         <v>46.37</v>
       </c>
       <c r="O13" t="n">
-        <v>3078241747750</v>
+        <v>3190060527500</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 요인으로 인한 증시 하락 및 '이재명 정부'에 대한 불만 토로. 낮은 주가와 실적 간의 괴리에 대한 불만.</t>
+          <t>레버리지 규제 및 이재명 정부 정책에 대한 강한 불만 표출. 세계 최고 영업이익에도 주가 부양 없다는 비판.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['레버리지', '국장', '실적']</t>
+          <t>['레버리지', '영업이익', '주가부양']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1682,13 +1682,13 @@
         <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F14" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G14" t="n">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="H14" t="n">
         <v>27.68</v>
@@ -1708,13 +1708,13 @@
         <v>19500</v>
       </c>
       <c r="M14" t="n">
-        <v>18880</v>
+        <v>18850</v>
       </c>
       <c r="N14" t="n">
         <v>27.67</v>
       </c>
       <c r="O14" t="n">
-        <v>39289490245</v>
+        <v>40742546870</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>증권사 애널리스트 불신, 조선주 폭락 원인 규명 요구. 실적 발표 및 수주 관련 의구심.</t>
+          <t>조선주 폭락에 대한 불만과 증권사 애널리스트에 대한 불신. 선박 뉴스의 신뢰성 의문 제기 및 주가 하락에 대한 우려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['조선주', '실적 발표', '수주']</t>
+          <t>['조선주', '증권사', '주주환원']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16710</v>
+        <v>16700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.63%</t>
+          <t>'-3.69%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>544</v>
+        <v>569</v>
       </c>
       <c r="H15" t="n">
         <v>9.460000000000001</v>
@@ -1800,13 +1800,13 @@
         <v>17220</v>
       </c>
       <c r="M15" t="n">
-        <v>16700</v>
+        <v>16660</v>
       </c>
       <c r="N15" t="n">
         <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>37238195625</v>
+        <v>38924557615</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대우건설 주주들에게 공매도와 대차 해지의 중요성을 호소. 주가 조작 및 공매도에 대한 불만.</t>
+          <t>주가 조작, 공매도 과열, 연기금 및 삼성자산운용의 행태에 대한 강한 불신과 비판. 대차 해지의 중요성 강조.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '주가조작']</t>
+          <t>['주가조작', '공매도', '연기금']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>230000</v>
+        <v>229500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.56%</t>
+          <t>'-4.77%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>71</v>
       </c>
       <c r="G16" t="n">
-        <v>749</v>
+        <v>777</v>
       </c>
       <c r="H16" t="n">
         <v>3.47</v>
@@ -1898,7 +1898,7 @@
         <v>4.12</v>
       </c>
       <c r="O16" t="n">
-        <v>41364793750</v>
+        <v>41916459750</v>
       </c>
       <c r="P16" t="n">
         <v>1233000</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>삼천당제약, 아일리아 영업이익 전망 및 캐나다 세마 출시 기대감. 연기금 매수세와 공매도 금지 조치에 따른 상승 전망.</t>
+          <t>공매도 과열 예상 속 연기금 7일 연속 매수. 캐나다 세마 출시 기대감 및 릴레이 계약 공시 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['아일리아', '영업이익', '공매도금지']</t>
+          <t>['공매도', '계약공시', '수급']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28200</v>
+        <v>28150</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.37%</t>
+          <t>'-5.54%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.76</v>
       </c>
       <c r="E17" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H17" t="n">
         <v>10.02</v>
@@ -1990,7 +1990,7 @@
         <v>10.78</v>
       </c>
       <c r="O17" t="n">
-        <v>58451895025</v>
+        <v>59952563900</v>
       </c>
       <c r="P17" t="n">
         <v>75900</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16880</v>
+        <v>16920</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.91%</t>
+          <t>'-5.69%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.95</v>
       </c>
       <c r="E18" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F18" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G18" t="n">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="H18" t="n">
         <v>3.97</v>
@@ -2082,7 +2082,7 @@
         <v>4.92</v>
       </c>
       <c r="O18" t="n">
-        <v>90962801640</v>
+        <v>92008705160</v>
       </c>
       <c r="P18" t="n">
         <v>31500</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 하락에 따른 대한광통신의 우려. 외인 및 기관 쌍매도, 프로그램 매매 불안감 언급.</t>
+          <t>미국 광통신주 하락세 속에서 대한광통신 주가 부진. 외인과 기관의 쌍매도 관찰.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신', '수급', '공매도']</t>
+          <t>['광통신', '수급', '매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>75400</v>
+        <v>75450</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.34%</t>
+          <t>'-6.27%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="F19" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G19" t="n">
-        <v>1192</v>
+        <v>1226</v>
       </c>
       <c r="H19" t="n">
         <v>22.49</v>
@@ -2174,7 +2174,7 @@
         <v>22.59</v>
       </c>
       <c r="O19" t="n">
-        <v>191974582950</v>
+        <v>197051913050</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 해외 가스 발전 수주 기대감에도 불구하고 주가 하락에 대한 답답함 표출. 공매도 및 주가 하락 원인에 대한 의문 제기.</t>
+          <t>한미 텍사스 가스발전 확정 소식에 따른 기대감과 함께, 원전 및 건설 관련 정치적 이슈에 대한 우려와 공매도에 대한 불만.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['가스발전', '주가하락', '공매도']</t>
+          <t>['가스발전', '원전', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7210</v>
+        <v>7230</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.80%</t>
+          <t>'-7.54%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-2.03</v>
       </c>
       <c r="E20" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F20" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G20" t="n">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="H20" t="n">
         <v>3.09</v>
@@ -2260,13 +2260,13 @@
         <v>8510</v>
       </c>
       <c r="M20" t="n">
-        <v>7170</v>
+        <v>7140</v>
       </c>
       <c r="N20" t="n">
         <v>5.12</v>
       </c>
       <c r="O20" t="n">
-        <v>82619437510</v>
+        <v>83613791170</v>
       </c>
       <c r="P20" t="n">
         <v>23500</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>삼표시멘트의 본PF 구성 및 대주단 구성 관련 정보 언급. 주가 흐름에 대한 분석 및 주의 촉구.</t>
+          <t>본PF 및 대주단 구성에 대한 언급과 함께, 주가 하락에 대한 불만. 부동산 시장과의 연관성 및 과거 유사 주포 운전 방식 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['본PF', '대주단', '주포']</t>
+          <t>['본PF', '대주단', '부동산주']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4790</v>
+        <v>4800</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-8.06%</t>
+          <t>'-7.87%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2329,7 +2329,7 @@
         <v>93</v>
       </c>
       <c r="F21" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G21" t="n">
         <v>326</v>
@@ -2358,7 +2358,7 @@
         <v>4.72</v>
       </c>
       <c r="O21" t="n">
-        <v>66756965598</v>
+        <v>67630671378</v>
       </c>
       <c r="P21" t="n">
         <v>8100</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>전환사채 발행 및 장내 매도 물량 부담으로 인한 초대형 악재 발생, 주가 급락에 대한 경고와 속지 말자는 주장.</t>
+          <t>전환사채 발행 및 장내 매도에 대한 우려. 광트랜시버 사업 전망에 대한 기대와 함께 급등 가능성에 대한 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['전환사채', '악재', '장내매도']</t>
+          <t>['전환사채', '광트랜시버', '장내매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2403,184 +2403,184 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52600</v>
+        <v>15160</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.47%</t>
+          <t>'-9.28%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.02</v>
+        <v>-1.44</v>
       </c>
       <c r="E22" t="n">
-        <v>301</v>
+        <v>60</v>
       </c>
       <c r="F22" t="n">
-        <v>150</v>
+        <v>38</v>
       </c>
       <c r="G22" t="n">
-        <v>615</v>
+        <v>194</v>
       </c>
       <c r="H22" t="n">
-        <v>1.32</v>
+        <v>0.93</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>58100</v>
+        <v>16710</v>
       </c>
       <c r="K22" t="n">
-        <v>63200</v>
+        <v>16460</v>
       </c>
       <c r="L22" t="n">
-        <v>63800</v>
+        <v>17180</v>
       </c>
       <c r="M22" t="n">
-        <v>52500</v>
+        <v>14820</v>
       </c>
       <c r="N22" t="n">
-        <v>1.3</v>
+        <v>2.37</v>
       </c>
       <c r="O22" t="n">
-        <v>53239790050</v>
+        <v>34337221010</v>
       </c>
       <c r="P22" t="n">
-        <v>63800</v>
+        <v>17590</v>
       </c>
       <c r="Q22" t="n">
-        <v>25600</v>
+        <v>6320</v>
       </c>
       <c r="R22" t="n">
-        <v>-173000</v>
+        <v>12000</v>
       </c>
       <c r="S22" t="n">
-        <v>-30000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>한미사이언스의 미국 비만주 급등과 비교하며 국내 시장 석권 준비 완료 언급. 승인 및 기술수출에도 급락하는 주가에 대한 불만.</t>
+          <t>KDB생명 해킹 방어 성공 및 AI 사이버보안 협의체 선정 뉴스. SKT와의 협력 기반 역대 고점 돌파 기대.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['비만치료제', '기술수출', '공매도']</t>
+          <t>['양자보안', 'AI', '사이버보안']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15050</v>
+        <v>52000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-9.93%</t>
+          <t>'-10.50%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-1.44</v>
+        <v>0.02</v>
       </c>
       <c r="E23" t="n">
-        <v>60</v>
+        <v>308</v>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>151</v>
       </c>
       <c r="G23" t="n">
-        <v>191</v>
+        <v>629</v>
       </c>
       <c r="H23" t="n">
-        <v>0.93</v>
+        <v>1.32</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>16710</v>
+        <v>58100</v>
       </c>
       <c r="K23" t="n">
-        <v>16460</v>
+        <v>63200</v>
       </c>
       <c r="L23" t="n">
-        <v>17180</v>
+        <v>63800</v>
       </c>
       <c r="M23" t="n">
-        <v>14820</v>
+        <v>51700</v>
       </c>
       <c r="N23" t="n">
-        <v>2.37</v>
+        <v>1.3</v>
       </c>
       <c r="O23" t="n">
-        <v>34161131580</v>
+        <v>54820857500</v>
       </c>
       <c r="P23" t="n">
-        <v>17590</v>
+        <v>63800</v>
       </c>
       <c r="Q23" t="n">
-        <v>6320</v>
+        <v>25600</v>
       </c>
       <c r="R23" t="n">
-        <v>12000</v>
+        <v>-173000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>KDB생명 해킹 방어 성공 및 AI 사이버보안 협의체 선정 뉴스. SKT와의 협력 기반 역대 고점 돌파 기대.</t>
+          <t>비만주 급등 속 한미사이언스 주가 급락. 식약처 승인에도 이해 안 되는 하락, 주가 조작 및 차명거래 의혹 제기.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['양자보안', 'AI', '사이버보안']</t>
+          <t>['비만주', '주가조작', '기술수출']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9830</v>
+        <v>9850</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.72%</t>
+          <t>'-10.54%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F24" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G24" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H24" t="n">
         <v>5.04</v>
@@ -2634,7 +2634,7 @@
         <v>5.01</v>
       </c>
       <c r="O24" t="n">
-        <v>6970537525</v>
+        <v>7036070640</v>
       </c>
       <c r="P24" t="n">
         <v>15900</v>

--- a/data/trending_integrated_20261008_13.xlsx
+++ b/data/trending_integrated_20261008_13.xlsx
@@ -584,7 +584,7 @@
         <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31048062260</v>
+        <v>31050996410</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11490</v>
+        <v>11410</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.30%</t>
+          <t>'+15.49%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
         <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="H3" t="n">
         <v>37.45</v>
@@ -702,7 +702,7 @@
         <v>37.41</v>
       </c>
       <c r="O3" t="n">
-        <v>63011352070</v>
+        <v>63443624860</v>
       </c>
       <c r="P3" t="n">
         <v>19150</v>
@@ -747,79 +747,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>비아트론</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13250</v>
+        <v>66200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.51%</t>
+          <t>'+14.73%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.23</v>
+        <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>85</v>
+        <v>322</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>154</v>
       </c>
       <c r="G4" t="n">
-        <v>163</v>
+        <v>644</v>
       </c>
       <c r="H4" t="n">
-        <v>4.43</v>
+        <v>1.32</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>11990</v>
+        <v>57700</v>
       </c>
       <c r="K4" t="n">
-        <v>14330</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>14980</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>13070</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.66</v>
+        <v>1.3</v>
       </c>
       <c r="O4" t="n">
-        <v>45620874775</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>14980</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-3000</v>
+        <v>-173000</v>
       </c>
       <c r="S4" t="n">
-        <v>-5000</v>
+        <v>-30000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>유리기판 공정용 글라스본더 개발 완료. 삼성전기 공동 개발, 동종 업체 대비 월등한 실적 및 낮은 시총 언급.</t>
+          <t>미국 비만주 급등과 대조적인 국내 시장 움직임 비판. 식약처 승인에도 불구하고 급락한 이유에 대한 의문 제기 및 주가 조작 의심. 유통 물량 대비 이해하기 어려운 주가 하락.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['글라스본더', '유리기판', '공동개발']</t>
+          <t>['비만약', '기술수출', '주가 조작']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>141000</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>비아트론</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14630</v>
+        <v>13250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.09%</t>
+          <t>'+10.51%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.15</v>
+        <v>-0.23</v>
       </c>
       <c r="E5" t="n">
-        <v>476</v>
+        <v>85</v>
       </c>
       <c r="F5" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>1384</v>
+        <v>160</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09</v>
+        <v>4.43</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13790</v>
+        <v>11990</v>
       </c>
       <c r="K5" t="n">
-        <v>13410</v>
+        <v>14330</v>
       </c>
       <c r="L5" t="n">
-        <v>15800</v>
+        <v>14980</v>
       </c>
       <c r="M5" t="n">
-        <v>11600</v>
+        <v>13070</v>
       </c>
       <c r="N5" t="n">
-        <v>0.24</v>
+        <v>4.66</v>
       </c>
       <c r="O5" t="n">
-        <v>137092875750</v>
+        <v>46127732800</v>
       </c>
       <c r="P5" t="n">
-        <v>28700</v>
+        <v>14980</v>
       </c>
       <c r="Q5" t="n">
-        <v>11600</v>
+        <v>6500</v>
       </c>
       <c r="R5" t="n">
-        <v>26000</v>
+        <v>-3000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>중복 상장 금지 예외 허용 및 무차별 공매도에 대한 강한 불만. 사기 상장 의혹 제기와 함께 주가 하락에 대한 우려.</t>
+          <t>유리기판 공정용 글라스본더 개발 완료 및 삼성전기와의 공동 개발 사실 강조. 대당 50억의 고가 장비로 수천억 매출 발생 가능성 및 향후 BPS, 배당률 비교 우위 분석. 유리기판 신대장주 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['중복상장', '공매도', '사기상장']</t>
+          <t>['글라스본더', '유리기판', '삼성전기']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>141000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38250</v>
+        <v>15140</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.66%</t>
+          <t>'+9.79%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>498</v>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>231</v>
       </c>
       <c r="G6" t="n">
-        <v>183</v>
+        <v>1399</v>
       </c>
       <c r="H6" t="n">
-        <v>31.86</v>
+        <v>0.09</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>36200</v>
+        <v>13790</v>
       </c>
       <c r="K6" t="n">
-        <v>36250</v>
+        <v>13410</v>
       </c>
       <c r="L6" t="n">
-        <v>39850</v>
+        <v>15800</v>
       </c>
       <c r="M6" t="n">
-        <v>36000</v>
+        <v>11600</v>
       </c>
       <c r="N6" t="n">
-        <v>31.78</v>
+        <v>0.24</v>
       </c>
       <c r="O6" t="n">
-        <v>120644692500</v>
+        <v>146132190135</v>
       </c>
       <c r="P6" t="n">
-        <v>45000</v>
+        <v>28700</v>
       </c>
       <c r="Q6" t="n">
-        <v>15530</v>
+        <v>11600</v>
       </c>
       <c r="R6" t="n">
-        <v>221000</v>
+        <v>26000</v>
       </c>
       <c r="S6" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>하락장 속 고영 주가 선방. JP모건의 미친듯한 매수세 확인, 추세 긍정적 평가. 외국인 순매수세 관찰.</t>
+          <t>국민권익위 및 금감원 신고 언급과 함께, 사기 상장 및 무차별 공매도에 대한 강한 비판. 중복 상장 허용 및 정부의 무능함에 대한 불만 표출. 악질적인 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외국인', '매수세', '추세']</t>
+          <t>['공매도', '사기 상장', '국민권익위']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6750</v>
+        <v>38200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.49%</t>
+          <t>'+5.52%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.31</v>
+        <v>0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>31.86</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6460</v>
+        <v>36200</v>
       </c>
       <c r="K7" t="n">
-        <v>6930</v>
+        <v>36250</v>
       </c>
       <c r="L7" t="n">
-        <v>8390</v>
+        <v>39850</v>
       </c>
       <c r="M7" t="n">
-        <v>6730</v>
+        <v>36000</v>
       </c>
       <c r="N7" t="n">
-        <v>0.31</v>
+        <v>31.78</v>
       </c>
       <c r="O7" t="n">
-        <v>20761354465</v>
+        <v>121345181925</v>
       </c>
       <c r="P7" t="n">
-        <v>9680</v>
+        <v>45000</v>
       </c>
       <c r="Q7" t="n">
-        <v>371</v>
+        <v>15530</v>
       </c>
       <c r="R7" t="n">
-        <v>-27000</v>
+        <v>221000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>관리종목 해제 및 거래 정상화 호재. 새 주인 확정 기대감 속 주포 움직임 주시, 재료 소멸 가능성 언급.</t>
+          <t>외인/기관 매수세 유입과 추세적 상승 기대감. 장 중 하락에도 불구하고 4만원 안착 시 긍정적 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['관리종목', '거래정상화', '주포']</t>
+          <t>['외국인', '기관', '추세']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13110</v>
+        <v>6740</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.30%</t>
+          <t>'+4.33%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="F8" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="H8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>12570</v>
+        <v>6460</v>
       </c>
       <c r="K8" t="n">
-        <v>12970</v>
+        <v>6930</v>
       </c>
       <c r="L8" t="n">
-        <v>14200</v>
+        <v>8390</v>
       </c>
       <c r="M8" t="n">
-        <v>12500</v>
+        <v>6730</v>
       </c>
       <c r="N8" t="n">
-        <v>1.88</v>
+        <v>0.31</v>
       </c>
       <c r="O8" t="n">
-        <v>83453873915</v>
+        <v>20804778435</v>
       </c>
       <c r="P8" t="n">
-        <v>22250</v>
+        <v>9680</v>
       </c>
       <c r="Q8" t="n">
-        <v>6000</v>
+        <v>371</v>
       </c>
       <c r="R8" t="n">
-        <v>-501000</v>
+        <v>-27000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>유증 물량 정리 및 1차 목표가 3만원 제시. 바이오스텝과의 연관성을 언급하며 상승 가능성에 대한 기대감 표현.</t>
+          <t>관리종목 해제 및 거래 정상화, 새 주인 확정 가능성 언급. 회사 미래 가치 및 불확실성 해소에 따른 긍정적 전망. 주포의 움직임 및 매물대 돌파 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['유증', '목표주가', '바이오스텝']</t>
+          <t>['관리종목 해제', '새 주인', '불확실성 해소']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4430</v>
+        <v>13100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+4.22%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.19</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F9" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G9" t="n">
-        <v>178</v>
+        <v>228</v>
       </c>
       <c r="H9" t="n">
-        <v>4.46</v>
+        <v>1.07</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>4430</v>
+        <v>12570</v>
       </c>
       <c r="K9" t="n">
-        <v>4650</v>
+        <v>12970</v>
       </c>
       <c r="L9" t="n">
-        <v>4855</v>
+        <v>14200</v>
       </c>
       <c r="M9" t="n">
-        <v>4185</v>
+        <v>12500</v>
       </c>
       <c r="N9" t="n">
-        <v>3.27</v>
+        <v>1.88</v>
       </c>
       <c r="O9" t="n">
-        <v>88015825743</v>
+        <v>83610927890</v>
       </c>
       <c r="P9" t="n">
-        <v>5470</v>
+        <v>22250</v>
       </c>
       <c r="Q9" t="n">
-        <v>2810</v>
+        <v>6000</v>
       </c>
       <c r="R9" t="n">
-        <v>-471000</v>
+        <v>-501000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>러시아 관련 국제 정세 불안으로 인한 전염병 확산 우려에 따른 제약주 관심 증가. 일부 주가 급등 소식은 있으나 팩트 기반 분석은 부족.</t>
+          <t>유증 물량 정리 확인 및 13500원 돌파 시 추가 상승 가능성 언급. 1차 목표가 3만원, 장기 목표주가 38,000원 제시. 공매도 관련 언급 및 바이오스텝과의 비교.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['전염병', '제약주', '국제정세']</t>
+          <t>['유증', '목표주가', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8230</v>
+        <v>4440</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.24%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.17</v>
+        <v>1.19</v>
       </c>
       <c r="E10" t="n">
+        <v>117</v>
+      </c>
+      <c r="F10" t="n">
         <v>81</v>
       </c>
-      <c r="F10" t="n">
-        <v>41</v>
-      </c>
       <c r="G10" t="n">
-        <v>255</v>
+        <v>180</v>
       </c>
       <c r="H10" t="n">
-        <v>26.38</v>
+        <v>4.46</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>8250</v>
+        <v>4430</v>
       </c>
       <c r="K10" t="n">
-        <v>8190</v>
+        <v>4650</v>
       </c>
       <c r="L10" t="n">
-        <v>8320</v>
+        <v>4855</v>
       </c>
       <c r="M10" t="n">
-        <v>8090</v>
+        <v>4185</v>
       </c>
       <c r="N10" t="n">
-        <v>26.55</v>
+        <v>3.27</v>
       </c>
       <c r="O10" t="n">
-        <v>15517760345</v>
+        <v>88302564733</v>
       </c>
       <c r="P10" t="n">
-        <v>17950</v>
+        <v>5470</v>
       </c>
       <c r="Q10" t="n">
-        <v>8090</v>
+        <v>2810</v>
       </c>
       <c r="R10" t="n">
-        <v>-51000</v>
+        <v>-471000</v>
       </c>
       <c r="S10" t="n">
-        <v>111000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>과도한 투자 대비 낮은 시가총액에 대한 비판과 경영 방식에 대한 의문. 공매도와 유증에 대한 부정적 인식.</t>
+          <t>WHO의 러시아 폐렴 상황 파악 지연 및 페스트 사망자 발생 관련 외신 보도 속, 전염병 심각 사태에 대한 약품 수요 기대감 존재. 그러나 구체적 근거 없이 분위기에 따른 기대 심리가 주를 이룸.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['시가총액', '공매도', '유증']</t>
+          <t>['전염병', 'WHO', '페스트']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45600</v>
+        <v>8250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.65%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.73</v>
+        <v>-0.17</v>
       </c>
       <c r="E11" t="n">
-        <v>305</v>
+        <v>82</v>
       </c>
       <c r="F11" t="n">
-        <v>166</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>1133</v>
+        <v>257</v>
       </c>
       <c r="H11" t="n">
-        <v>13.39</v>
+        <v>26.38</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>45900</v>
+        <v>8250</v>
       </c>
       <c r="K11" t="n">
-        <v>45950</v>
+        <v>8190</v>
       </c>
       <c r="L11" t="n">
-        <v>46500</v>
+        <v>8320</v>
       </c>
       <c r="M11" t="n">
-        <v>45100</v>
+        <v>8090</v>
       </c>
       <c r="N11" t="n">
-        <v>14.12</v>
+        <v>26.55</v>
       </c>
       <c r="O11" t="n">
-        <v>30936480250</v>
+        <v>15800876085</v>
       </c>
       <c r="P11" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q11" t="n">
-        <v>24150</v>
+        <v>8090</v>
       </c>
       <c r="R11" t="n">
-        <v>-66000</v>
+        <v>-51000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>111000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>HLB의 리보세라닙 병용요법 허가 기대감 및 2026년 연말 30만 목표 제시. 공매도 발악 및 숏스퀴즈 현실화 가능성 언급.</t>
+          <t>과도한 투자 대비 낮은 시가총액에 대한 비판과 경영 방식에 대한 의문. 공매도와 유증에 대한 부정적 인식.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['리보세라닙', '공매도', '숏스퀴즈']</t>
+          <t>['시가총액', '공매도', '유증']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1710000</v>
+        <v>45650</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.75%</t>
+          <t>'-0.54%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.12</v>
+        <v>-0.73</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>313</v>
       </c>
       <c r="F12" t="n">
-        <v>448</v>
+        <v>172</v>
       </c>
       <c r="G12" t="n">
-        <v>1525</v>
+        <v>1153</v>
       </c>
       <c r="H12" t="n">
-        <v>49.59</v>
+        <v>13.39</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1723000</v>
+        <v>45900</v>
       </c>
       <c r="K12" t="n">
-        <v>1722000</v>
+        <v>45950</v>
       </c>
       <c r="L12" t="n">
-        <v>1759000</v>
+        <v>46500</v>
       </c>
       <c r="M12" t="n">
-        <v>1692000</v>
+        <v>45100</v>
       </c>
       <c r="N12" t="n">
-        <v>49.71</v>
+        <v>14.12</v>
       </c>
       <c r="O12" t="n">
-        <v>3147694431500</v>
+        <v>31372311075</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>69200</v>
       </c>
       <c r="Q12" t="n">
-        <v>403000</v>
+        <v>24150</v>
       </c>
       <c r="R12" t="n">
-        <v>82000</v>
+        <v>-66000</v>
       </c>
       <c r="S12" t="n">
-        <v>-70000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>솔리다임 상장 및 중복 상장에 대한 비판과 정부 정책에 대한 불만. 주가 조작 의혹 제기.</t>
+          <t>HLB의 리보세라닙 병용요법 허가 기대감 및 2026년 연말 30만 목표 제시. 공매도 발악 및 숏스퀴즈 현실화 가능성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['솔리다임', '중복상장', '주가조작']</t>
+          <t>['리보세라닙', '공매도', '숏스퀴즈']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>264750</v>
+        <v>1712000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.40%</t>
+          <t>'-0.64%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="E13" t="n">
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>526</v>
+        <v>448</v>
       </c>
       <c r="G13" t="n">
-        <v>2058</v>
+        <v>1524</v>
       </c>
       <c r="H13" t="n">
-        <v>46.38</v>
+        <v>49.59</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>268500</v>
+        <v>1723000</v>
       </c>
       <c r="K13" t="n">
-        <v>269500</v>
+        <v>1722000</v>
       </c>
       <c r="L13" t="n">
-        <v>270000</v>
+        <v>1759000</v>
       </c>
       <c r="M13" t="n">
-        <v>263000</v>
+        <v>1692000</v>
       </c>
       <c r="N13" t="n">
-        <v>46.37</v>
+        <v>49.71</v>
       </c>
       <c r="O13" t="n">
-        <v>3190060527500</v>
+        <v>3202058537000</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>90200</v>
+        <v>403000</v>
       </c>
       <c r="R13" t="n">
-        <v>78000</v>
+        <v>82000</v>
       </c>
       <c r="S13" t="n">
-        <v>-934000</v>
+        <v>-70000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>레버리지 규제 및 이재명 정부 정책에 대한 강한 불만 표출. 세계 최고 영업이익에도 주가 부양 없다는 비판.</t>
+          <t>솔리다임 상장 관련 최태원 회장에 대한 비판과 함께, 이재명 정부 정책에 대한 부정적 평가. 외인 자사주 매입 후 매도 및 국장 주가 움직임에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['레버리지', '영업이익', '주가부양']</t>
+          <t>['솔리다임', '자사주 매입', '국장']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18890</v>
+        <v>265250</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.33%</t>
+          <t>'-1.21%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>131</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>74</v>
+        <v>530</v>
       </c>
       <c r="G14" t="n">
-        <v>360</v>
+        <v>2090</v>
       </c>
       <c r="H14" t="n">
-        <v>27.68</v>
+        <v>46.38</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>19540</v>
+        <v>268500</v>
       </c>
       <c r="K14" t="n">
-        <v>19490</v>
+        <v>269500</v>
       </c>
       <c r="L14" t="n">
-        <v>19500</v>
+        <v>270000</v>
       </c>
       <c r="M14" t="n">
-        <v>18850</v>
+        <v>263000</v>
       </c>
       <c r="N14" t="n">
-        <v>27.67</v>
+        <v>46.37</v>
       </c>
       <c r="O14" t="n">
-        <v>40742546870</v>
+        <v>3265662897500</v>
       </c>
       <c r="P14" t="n">
-        <v>35350</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>18440</v>
+        <v>90200</v>
       </c>
       <c r="R14" t="n">
-        <v>-451000</v>
+        <v>78000</v>
       </c>
       <c r="S14" t="n">
-        <v>-69000</v>
+        <v>-934000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>조선주 폭락에 대한 불만과 증권사 애널리스트에 대한 불신. 선박 뉴스의 신뢰성 의문 제기 및 주가 하락에 대한 우려.</t>
+          <t>이재명 정부의 레버리지 정책 비판과 함께, 분기 1000조 영업이익에도 불구하고 주가 부양 없는 국장 현실에 대한 강한 불만 표출. 실적과 무관한 주가 흐름에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['조선주', '증권사', '주주환원']</t>
+          <t>['레버리지', '영업이익', '주가 부양']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16700</v>
+        <v>18910</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.69%</t>
+          <t>'-3.22%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="F15" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="G15" t="n">
-        <v>569</v>
+        <v>358</v>
       </c>
       <c r="H15" t="n">
-        <v>9.460000000000001</v>
+        <v>27.68</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17340</v>
+        <v>19540</v>
       </c>
       <c r="K15" t="n">
-        <v>17190</v>
+        <v>19490</v>
       </c>
       <c r="L15" t="n">
-        <v>17220</v>
+        <v>19500</v>
       </c>
       <c r="M15" t="n">
-        <v>16660</v>
+        <v>18850</v>
       </c>
       <c r="N15" t="n">
-        <v>9.5</v>
+        <v>27.67</v>
       </c>
       <c r="O15" t="n">
-        <v>38924557615</v>
+        <v>41422300475</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>18440</v>
       </c>
       <c r="R15" t="n">
-        <v>-81000</v>
+        <v>-451000</v>
       </c>
       <c r="S15" t="n">
-        <v>-19000</v>
+        <v>-69000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 조작, 공매도 과열, 연기금 및 삼성자산운용의 행태에 대한 강한 불신과 비판. 대차 해지의 중요성 강조.</t>
+          <t>조선주 폭락의 주범으로 특정 세력 지목 및 애널리스트들의 추천 종목 손실 발생에 대한 비판. 선박 뉴스 신뢰도 의문 제기 및 페인트 회사 주가 미반영 등 실질적 근거 부족에 따른 부정적 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가조작', '공매도', '연기금']</t>
+          <t>['조선주', '폭락', '실적']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>229500</v>
+        <v>16710</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.77%</t>
+          <t>'-3.63%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.65</v>
+        <v>-0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="F16" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="G16" t="n">
-        <v>777</v>
+        <v>574</v>
       </c>
       <c r="H16" t="n">
-        <v>3.47</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>241000</v>
+        <v>17340</v>
       </c>
       <c r="K16" t="n">
-        <v>227000</v>
+        <v>17190</v>
       </c>
       <c r="L16" t="n">
-        <v>239500</v>
+        <v>17220</v>
       </c>
       <c r="M16" t="n">
-        <v>210500</v>
+        <v>16660</v>
       </c>
       <c r="N16" t="n">
-        <v>4.12</v>
+        <v>9.5</v>
       </c>
       <c r="O16" t="n">
-        <v>41916459750</v>
+        <v>39657508230</v>
       </c>
       <c r="P16" t="n">
-        <v>1233000</v>
+        <v>40350</v>
       </c>
       <c r="Q16" t="n">
-        <v>120000</v>
+        <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>6000</v>
+        <v>-81000</v>
       </c>
       <c r="S16" t="n">
-        <v>5000</v>
+        <v>-19000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>공매도 과열 예상 속 연기금 7일 연속 매수. 캐나다 세마 출시 기대감 및 릴레이 계약 공시 언급.</t>
+          <t>AI가 지목한 JP, 한국, 신한, 삼성증권 등 특정 기관 및 증권사에 대한 의혹 제기. 연기금 및 삼성자산운용의 움직임과 공매도에 대한 불만 표출, 주가 조작 및 개인 투자자 손실에 대한 우려.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공매도', '계약공시', '수급']</t>
+          <t>['공매도', '주가 조작', '연기금']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,86 +1936,86 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28150</v>
+        <v>230000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.54%</t>
+          <t>'-4.56%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.76</v>
+        <v>-0.65</v>
       </c>
       <c r="E17" t="n">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="G17" t="n">
-        <v>181</v>
+        <v>782</v>
       </c>
       <c r="H17" t="n">
-        <v>10.02</v>
+        <v>3.47</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>29800</v>
+        <v>241000</v>
       </c>
       <c r="K17" t="n">
-        <v>29900</v>
+        <v>227000</v>
       </c>
       <c r="L17" t="n">
-        <v>30000</v>
+        <v>239500</v>
       </c>
       <c r="M17" t="n">
-        <v>28050</v>
+        <v>210500</v>
       </c>
       <c r="N17" t="n">
-        <v>10.78</v>
+        <v>4.12</v>
       </c>
       <c r="O17" t="n">
-        <v>59952563900</v>
+        <v>42167273500</v>
       </c>
       <c r="P17" t="n">
-        <v>75900</v>
+        <v>1233000</v>
       </c>
       <c r="Q17" t="n">
-        <v>15960</v>
+        <v>120000</v>
       </c>
       <c r="R17" t="n">
-        <v>-560000</v>
+        <v>6000</v>
       </c>
       <c r="S17" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
+          <t>공매도 과열 예상 속 연기금 7일 연속 매수. 캐나다 세마 출시 기대감 및 릴레이 계약 공시 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '유상증자']</t>
+          <t>['공매도', '계약공시', '수급']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,174 +2023,174 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16920</v>
+        <v>28350</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.69%</t>
+          <t>'-4.87%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.95</v>
+        <v>-0.76</v>
       </c>
       <c r="E18" t="n">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="F18" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
-        <v>532</v>
+        <v>182</v>
       </c>
       <c r="H18" t="n">
-        <v>3.97</v>
+        <v>10.02</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>17940</v>
+        <v>29800</v>
       </c>
       <c r="K18" t="n">
-        <v>17770</v>
+        <v>29900</v>
       </c>
       <c r="L18" t="n">
-        <v>17940</v>
+        <v>30000</v>
       </c>
       <c r="M18" t="n">
-        <v>16750</v>
+        <v>28050</v>
       </c>
       <c r="N18" t="n">
-        <v>4.92</v>
+        <v>10.78</v>
       </c>
       <c r="O18" t="n">
-        <v>92008705160</v>
+        <v>60947358400</v>
       </c>
       <c r="P18" t="n">
-        <v>31500</v>
+        <v>75900</v>
       </c>
       <c r="Q18" t="n">
-        <v>1272</v>
+        <v>15960</v>
       </c>
       <c r="R18" t="n">
-        <v>-426000</v>
+        <v>-560000</v>
       </c>
       <c r="S18" t="n">
-        <v>-60000</v>
+        <v>1000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신주 하락세 속에서 대한광통신 주가 부진. 외인과 기관의 쌍매도 관찰.</t>
+          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신', '수급', '매도']</t>
+          <t>['주가 하락', '공매도', '유상증자']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>75450</v>
+        <v>16970</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.27%</t>
+          <t>'-5.41%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.1</v>
+        <v>-0.95</v>
       </c>
       <c r="E19" t="n">
-        <v>424</v>
+        <v>128</v>
       </c>
       <c r="F19" t="n">
-        <v>248</v>
+        <v>77</v>
       </c>
       <c r="G19" t="n">
-        <v>1226</v>
+        <v>532</v>
       </c>
       <c r="H19" t="n">
-        <v>22.49</v>
+        <v>3.97</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>80500</v>
+        <v>17940</v>
       </c>
       <c r="K19" t="n">
-        <v>79600</v>
+        <v>17770</v>
       </c>
       <c r="L19" t="n">
-        <v>79600</v>
+        <v>17940</v>
       </c>
       <c r="M19" t="n">
-        <v>75200</v>
+        <v>16750</v>
       </c>
       <c r="N19" t="n">
-        <v>22.59</v>
+        <v>4.92</v>
       </c>
       <c r="O19" t="n">
-        <v>197051913050</v>
+        <v>92704301300</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q19" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>-579000</v>
+        <v>-426000</v>
       </c>
       <c r="S19" t="n">
-        <v>-91000</v>
+        <v>-60000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>한미 텍사스 가스발전 확정 소식에 따른 기대감과 함께, 원전 및 건설 관련 정치적 이슈에 대한 우려와 공매도에 대한 불만.</t>
+          <t>미국 광통신주 하락세 속에서 대한광통신 주가 부진. 외인과 기관의 쌍매도 관찰.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['가스발전', '원전', '공매도']</t>
+          <t>['광통신', '수급', '매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,77 +2212,77 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7230</v>
+        <v>75600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-7.54%</t>
+          <t>'-6.09%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-2.03</v>
+        <v>-0.1</v>
       </c>
       <c r="E20" t="n">
-        <v>184</v>
+        <v>438</v>
       </c>
       <c r="F20" t="n">
-        <v>88</v>
+        <v>261</v>
       </c>
       <c r="G20" t="n">
-        <v>527</v>
+        <v>1254</v>
       </c>
       <c r="H20" t="n">
-        <v>3.09</v>
+        <v>22.49</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>7820</v>
+        <v>80500</v>
       </c>
       <c r="K20" t="n">
-        <v>8080</v>
+        <v>79600</v>
       </c>
       <c r="L20" t="n">
-        <v>8510</v>
+        <v>79600</v>
       </c>
       <c r="M20" t="n">
-        <v>7140</v>
+        <v>75200</v>
       </c>
       <c r="N20" t="n">
-        <v>5.12</v>
+        <v>22.59</v>
       </c>
       <c r="O20" t="n">
-        <v>83613791170</v>
+        <v>201137302000</v>
       </c>
       <c r="P20" t="n">
-        <v>23500</v>
+        <v>139200</v>
       </c>
       <c r="Q20" t="n">
-        <v>2890</v>
+        <v>57000</v>
       </c>
       <c r="R20" t="n">
-        <v>-518000</v>
+        <v>-579000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-91000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>본PF 및 대주단 구성에 대한 언급과 함께, 주가 하락에 대한 불만. 부동산 시장과의 연관성 및 과거 유사 주포 운전 방식 언급.</t>
+          <t>한미 텍사스 가스발전 확정 소식에 따른 기대감과 함께, 원전 및 건설 관련 정치적 이슈에 대한 우려와 공매도에 대한 불만.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['본PF', '대주단', '부동산주']</t>
+          <t>['가스발전', '원전', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4800</v>
+        <v>4822</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.87%</t>
+          <t>'-7.45%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2332,7 +2332,7 @@
         <v>61</v>
       </c>
       <c r="G21" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H21" t="n">
         <v>4.65</v>
@@ -2358,7 +2358,7 @@
         <v>4.72</v>
       </c>
       <c r="O21" t="n">
-        <v>67630671378</v>
+        <v>67905347683</v>
       </c>
       <c r="P21" t="n">
         <v>8100</v>
@@ -2403,31 +2403,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15160</v>
+        <v>7140</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.28%</t>
+          <t>'-8.70%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1.44</v>
+        <v>-2.03</v>
       </c>
       <c r="E22" t="n">
-        <v>60</v>
+        <v>191</v>
       </c>
       <c r="F22" t="n">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="G22" t="n">
-        <v>194</v>
+        <v>539</v>
       </c>
       <c r="H22" t="n">
-        <v>0.93</v>
+        <v>3.09</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,47 +2435,47 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>16710</v>
+        <v>7820</v>
       </c>
       <c r="K22" t="n">
-        <v>16460</v>
+        <v>8080</v>
       </c>
       <c r="L22" t="n">
-        <v>17180</v>
+        <v>8510</v>
       </c>
       <c r="M22" t="n">
-        <v>14820</v>
+        <v>7130</v>
       </c>
       <c r="N22" t="n">
-        <v>2.37</v>
+        <v>5.12</v>
       </c>
       <c r="O22" t="n">
-        <v>34337221010</v>
+        <v>84103923020</v>
       </c>
       <c r="P22" t="n">
-        <v>17590</v>
+        <v>23500</v>
       </c>
       <c r="Q22" t="n">
-        <v>6320</v>
+        <v>2890</v>
       </c>
       <c r="R22" t="n">
-        <v>12000</v>
+        <v>-518000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>KDB생명 해킹 방어 성공 및 AI 사이버보안 협의체 선정 뉴스. SKT와의 협력 기반 역대 고점 돌파 기대.</t>
+          <t>본PF 및 대주단 구성에 대한 언급과 함께, 주가 하락에 대한 불만. 부동산 시장과의 연관성 및 과거 유사 주포 운전 방식 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['양자보안', 'AI', '사이버보안']</t>
+          <t>['본PF', '대주단', '부동산주']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2483,104 +2483,104 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52000</v>
+        <v>15180</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-10.50%</t>
+          <t>'-9.16%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.02</v>
+        <v>-1.44</v>
       </c>
       <c r="E23" t="n">
-        <v>308</v>
+        <v>60</v>
       </c>
       <c r="F23" t="n">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="G23" t="n">
-        <v>629</v>
+        <v>194</v>
       </c>
       <c r="H23" t="n">
-        <v>1.32</v>
+        <v>0.93</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>58100</v>
+        <v>16710</v>
       </c>
       <c r="K23" t="n">
-        <v>63200</v>
+        <v>16460</v>
       </c>
       <c r="L23" t="n">
-        <v>63800</v>
+        <v>17180</v>
       </c>
       <c r="M23" t="n">
-        <v>51700</v>
+        <v>14820</v>
       </c>
       <c r="N23" t="n">
-        <v>1.3</v>
+        <v>2.37</v>
       </c>
       <c r="O23" t="n">
-        <v>54820857500</v>
+        <v>34456022490</v>
       </c>
       <c r="P23" t="n">
-        <v>63800</v>
+        <v>17590</v>
       </c>
       <c r="Q23" t="n">
-        <v>25600</v>
+        <v>6320</v>
       </c>
       <c r="R23" t="n">
-        <v>-173000</v>
+        <v>12000</v>
       </c>
       <c r="S23" t="n">
-        <v>-30000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>비만주 급등 속 한미사이언스 주가 급락. 식약처 승인에도 이해 안 되는 하락, 주가 조작 및 차명거래 의혹 제기.</t>
+          <t>KDB생명 해킹 방어 성공 및 AI 사이버보안 협의체 선정 뉴스. SKT와의 협력 기반 역대 고점 돌파 기대.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['비만주', '주가조작', '기술수출']</t>
+          <t>['양자보안', 'AI', '사이버보안']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9850</v>
+        <v>9830</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.54%</t>
+          <t>'-10.72%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F24" t="n">
         <v>64</v>
       </c>
       <c r="G24" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H24" t="n">
         <v>5.04</v>
@@ -2634,7 +2634,7 @@
         <v>5.01</v>
       </c>
       <c r="O24" t="n">
-        <v>7036070640</v>
+        <v>7134112810</v>
       </c>
       <c r="P24" t="n">
         <v>15900</v>

--- a/data/trending_integrated_20261008_13.xlsx
+++ b/data/trending_integrated_20261008_13.xlsx
@@ -578,13 +578,13 @@
         <v>-0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31050996410</v>
+        <v>31054548940</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11410</v>
+        <v>11530</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.49%</t>
+          <t>'+16.70%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
         <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H3" t="n">
         <v>37.45</v>
@@ -702,7 +702,7 @@
         <v>37.41</v>
       </c>
       <c r="O3" t="n">
-        <v>63443624860</v>
+        <v>64144091430</v>
       </c>
       <c r="P3" t="n">
         <v>19150</v>
@@ -747,79 +747,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>비아트론</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66200</v>
+        <v>13660</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.73%</t>
+          <t>'+13.93%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.02</v>
+        <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>322</v>
+        <v>86</v>
       </c>
       <c r="F4" t="n">
-        <v>154</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>644</v>
+        <v>160</v>
       </c>
       <c r="H4" t="n">
-        <v>1.32</v>
+        <v>4.43</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>57700</v>
+        <v>11990</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>14330</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>14980</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>13070</v>
       </c>
       <c r="N4" t="n">
-        <v>1.3</v>
+        <v>4.66</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>46587656760</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>14980</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="R4" t="n">
-        <v>-173000</v>
+        <v>-3000</v>
       </c>
       <c r="S4" t="n">
-        <v>-30000</v>
+        <v>-5000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>미국 비만주 급등과 대조적인 국내 시장 움직임 비판. 식약처 승인에도 불구하고 급락한 이유에 대한 의문 제기 및 주가 조작 의심. 유통 물량 대비 이해하기 어려운 주가 하락.</t>
+          <t>유리기판 공정용 글라스본더 개발 완료 및 삼성전기와의 공동 개발 사실 강조. 대당 50억의 고가 장비로 수천억 매출 발생 가능성 및 향후 BPS, 배당률 비교 우위 분석. 유리기판 신대장주 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['비만약', '기술수출', '주가 조작']</t>
+          <t>['글라스본더', '유리기판', '삼성전기']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>141000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>비아트론</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13250</v>
+        <v>15250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.51%</t>
+          <t>'+10.59%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.23</v>
+        <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>85</v>
+        <v>536</v>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>241</v>
       </c>
       <c r="G5" t="n">
-        <v>160</v>
+        <v>1438</v>
       </c>
       <c r="H5" t="n">
-        <v>4.43</v>
+        <v>0.09</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>11990</v>
+        <v>13790</v>
       </c>
       <c r="K5" t="n">
-        <v>14330</v>
+        <v>13410</v>
       </c>
       <c r="L5" t="n">
-        <v>14980</v>
+        <v>15960</v>
       </c>
       <c r="M5" t="n">
-        <v>13070</v>
+        <v>11600</v>
       </c>
       <c r="N5" t="n">
-        <v>4.66</v>
+        <v>0.24</v>
       </c>
       <c r="O5" t="n">
-        <v>46127732800</v>
+        <v>169419787075</v>
       </c>
       <c r="P5" t="n">
-        <v>14980</v>
+        <v>28700</v>
       </c>
       <c r="Q5" t="n">
-        <v>6500</v>
+        <v>11600</v>
       </c>
       <c r="R5" t="n">
-        <v>-3000</v>
+        <v>26000</v>
       </c>
       <c r="S5" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>유리기판 공정용 글라스본더 개발 완료 및 삼성전기와의 공동 개발 사실 강조. 대당 50억의 고가 장비로 수천억 매출 발생 가능성 및 향후 BPS, 배당률 비교 우위 분석. 유리기판 신대장주 기대감.</t>
+          <t>덕산넵코어스의 상장 및 주가 움직임에 대한 불만과 금감원 신고, 국민권익위 조사 요청 등 불공정 거래 의혹 및 정부 무능에 대한 비판이 제기됨.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['글라스본더', '유리기판', '삼성전기']</t>
+          <t>['덕산넵코어스', '불공정 거래', '상장']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>141000</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15140</v>
+        <v>38100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.79%</t>
+          <t>'+5.25%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.15</v>
+        <v>0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>498</v>
+        <v>85</v>
       </c>
       <c r="F6" t="n">
-        <v>231</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>1399</v>
+        <v>191</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09</v>
+        <v>31.86</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13790</v>
+        <v>36200</v>
       </c>
       <c r="K6" t="n">
-        <v>13410</v>
+        <v>36250</v>
       </c>
       <c r="L6" t="n">
-        <v>15800</v>
+        <v>39850</v>
       </c>
       <c r="M6" t="n">
-        <v>11600</v>
+        <v>36000</v>
       </c>
       <c r="N6" t="n">
-        <v>0.24</v>
+        <v>31.78</v>
       </c>
       <c r="O6" t="n">
-        <v>146132190135</v>
+        <v>122429871325</v>
       </c>
       <c r="P6" t="n">
-        <v>28700</v>
+        <v>45000</v>
       </c>
       <c r="Q6" t="n">
-        <v>11600</v>
+        <v>15530</v>
       </c>
       <c r="R6" t="n">
-        <v>26000</v>
+        <v>221000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>국민권익위 및 금감원 신고 언급과 함께, 사기 상장 및 무차별 공매도에 대한 강한 비판. 중복 상장 허용 및 정부의 무능함에 대한 불만 표출. 악질적인 주가 조작 의혹 제기.</t>
+          <t>JP모건의 매수세와 기관/외국인 매수 물량이 긍정적. 현재 추세와 하락장 속에서의 강한 버팀목 역할 분석.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공매도', '사기 상장', '국민권익위']</t>
+          <t>['기관 매수', '외국인 매수', '추세']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38200</v>
+        <v>13100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.52%</t>
+          <t>'+4.22%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.08</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G7" t="n">
-        <v>186</v>
+        <v>227</v>
       </c>
       <c r="H7" t="n">
-        <v>31.86</v>
+        <v>1.07</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>36200</v>
+        <v>12570</v>
       </c>
       <c r="K7" t="n">
-        <v>36250</v>
+        <v>12970</v>
       </c>
       <c r="L7" t="n">
-        <v>39850</v>
+        <v>14200</v>
       </c>
       <c r="M7" t="n">
-        <v>36000</v>
+        <v>12500</v>
       </c>
       <c r="N7" t="n">
-        <v>31.78</v>
+        <v>1.88</v>
       </c>
       <c r="O7" t="n">
-        <v>121345181925</v>
+        <v>84226437195</v>
       </c>
       <c r="P7" t="n">
-        <v>45000</v>
+        <v>22250</v>
       </c>
       <c r="Q7" t="n">
-        <v>15530</v>
+        <v>6000</v>
       </c>
       <c r="R7" t="n">
-        <v>221000</v>
+        <v>-501000</v>
       </c>
       <c r="S7" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>외인/기관 매수세 유입과 추세적 상승 기대감. 장 중 하락에도 불구하고 4만원 안착 시 긍정적 전망.</t>
+          <t>HLB제약의 주가 상승 기대감과 목표 주가 제시가 있으나, 일부에서는 주가 움직임이 답답하다는 의견과 함께 유증 물량 정리 및 공매도 관련 논의가 있음.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외국인', '기관', '추세']</t>
+          <t>['HLB제약', '목표 주가', '유증']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6740</v>
+        <v>6720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.33%</t>
+          <t>'+4.02%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" t="n">
         <v>193</v>
@@ -1156,13 +1156,13 @@
         <v>8390</v>
       </c>
       <c r="M8" t="n">
-        <v>6730</v>
+        <v>6720</v>
       </c>
       <c r="N8" t="n">
         <v>0.31</v>
       </c>
       <c r="O8" t="n">
-        <v>20804778435</v>
+        <v>20916343100</v>
       </c>
       <c r="P8" t="n">
         <v>9680</v>
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13100</v>
+        <v>8260</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.22%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.17</v>
       </c>
       <c r="E9" t="n">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="H9" t="n">
-        <v>1.07</v>
+        <v>26.38</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>12570</v>
+        <v>8250</v>
       </c>
       <c r="K9" t="n">
-        <v>12970</v>
+        <v>8190</v>
       </c>
       <c r="L9" t="n">
-        <v>14200</v>
+        <v>8320</v>
       </c>
       <c r="M9" t="n">
-        <v>12500</v>
+        <v>8090</v>
       </c>
       <c r="N9" t="n">
-        <v>1.88</v>
+        <v>26.55</v>
       </c>
       <c r="O9" t="n">
-        <v>83610927890</v>
+        <v>16241909100</v>
       </c>
       <c r="P9" t="n">
-        <v>22250</v>
+        <v>17950</v>
       </c>
       <c r="Q9" t="n">
-        <v>6000</v>
+        <v>8090</v>
       </c>
       <c r="R9" t="n">
-        <v>-501000</v>
+        <v>-51000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>111000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>유증 물량 정리 확인 및 13500원 돌파 시 추가 상승 가능성 언급. 1차 목표가 3만원, 장기 목표주가 38,000원 제시. 공매도 관련 언급 및 바이오스텝과의 비교.</t>
+          <t>과도한 투자 대비 낮은 시가총액에 대한 비판과 경영 방식에 대한 의문. 공매도와 유증에 대한 부정적 인식.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['유증', '목표주가', '공매도']</t>
+          <t>['시가총액', '공매도', '유증']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4440</v>
+        <v>4435</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.11%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>1.19</v>
       </c>
       <c r="E10" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G10" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="H10" t="n">
         <v>4.46</v>
@@ -1346,7 +1346,7 @@
         <v>3.27</v>
       </c>
       <c r="O10" t="n">
-        <v>88302564733</v>
+        <v>88669828325</v>
       </c>
       <c r="P10" t="n">
         <v>5470</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>WHO의 러시아 폐렴 상황 파악 지연 및 페스트 사망자 발생 관련 외신 보도 속, 전염병 심각 사태에 대한 약품 수요 기대감 존재. 그러나 구체적 근거 없이 분위기에 따른 기대 심리가 주를 이룸.</t>
+          <t>러시아발 전염병 관련 보도와 미국 항생제 회사 주가 폭등 속에서 국제약품에 대한 기대감이 나타나고 있으나, 구체적인 사실 기반의 분석은 부족함.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['전염병', 'WHO', '페스트']</t>
+          <t>['전염병', '항생제', '속보']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8250</v>
+        <v>1716000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.41%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.17</v>
+        <v>-0.12</v>
       </c>
       <c r="E11" t="n">
-        <v>82</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>456</v>
       </c>
       <c r="G11" t="n">
-        <v>257</v>
+        <v>1526</v>
       </c>
       <c r="H11" t="n">
-        <v>26.38</v>
+        <v>49.59</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8250</v>
+        <v>1723000</v>
       </c>
       <c r="K11" t="n">
-        <v>8190</v>
+        <v>1722000</v>
       </c>
       <c r="L11" t="n">
-        <v>8320</v>
+        <v>1759000</v>
       </c>
       <c r="M11" t="n">
-        <v>8090</v>
+        <v>1692000</v>
       </c>
       <c r="N11" t="n">
-        <v>26.55</v>
+        <v>49.71</v>
       </c>
       <c r="O11" t="n">
-        <v>15800876085</v>
+        <v>3252074239500</v>
       </c>
       <c r="P11" t="n">
-        <v>17950</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>8090</v>
+        <v>403000</v>
       </c>
       <c r="R11" t="n">
-        <v>-51000</v>
+        <v>82000</v>
       </c>
       <c r="S11" t="n">
-        <v>111000</v>
+        <v>-70000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>과도한 투자 대비 낮은 시가총액에 대한 비판과 경영 방식에 대한 의문. 공매도와 유증에 대한 부정적 인식.</t>
+          <t>SK하이닉스의 주가 하락과 솔리다임 상장 이슈에 대한 불만이 제기되며, 정부 정책 및 경영진에 대한 비판과 함께 투자 철수 의사를 밝히는 의견들이 나타남.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['시가총액', '공매도', '유증']</t>
+          <t>['SK하이닉스', '솔리다임', '주가 하락']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45650</v>
+        <v>45550</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.54%</t>
+          <t>'-0.76%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.73</v>
       </c>
       <c r="E12" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F12" t="n">
         <v>172</v>
       </c>
       <c r="G12" t="n">
-        <v>1153</v>
+        <v>1178</v>
       </c>
       <c r="H12" t="n">
         <v>13.39</v>
@@ -1530,7 +1530,7 @@
         <v>14.12</v>
       </c>
       <c r="O12" t="n">
-        <v>31372311075</v>
+        <v>31911575025</v>
       </c>
       <c r="P12" t="n">
         <v>69200</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>HLB의 리보세라닙 병용요법 허가 기대감 및 2026년 연말 30만 목표 제시. 공매도 발악 및 숏스퀴즈 현실화 가능성 언급.</t>
+          <t>HLB의 리보세라닙 병용요법 허가 기대감과 2026년 연말 30만 목표 주가가 언급되며, 공매도 세력에 대한 경고와 함께 무상증자 및 신한증권 관련 논의가 있음.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['리보세라닙', '공매도', '숏스퀴즈']</t>
+          <t>['HLB', '리보세라닙', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1712000</v>
+        <v>265750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.64%</t>
+          <t>'-1.02%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.12</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>448</v>
+        <v>531</v>
       </c>
       <c r="G13" t="n">
-        <v>1524</v>
+        <v>2104</v>
       </c>
       <c r="H13" t="n">
-        <v>49.59</v>
+        <v>46.38</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1723000</v>
+        <v>268500</v>
       </c>
       <c r="K13" t="n">
-        <v>1722000</v>
+        <v>269500</v>
       </c>
       <c r="L13" t="n">
-        <v>1759000</v>
+        <v>270000</v>
       </c>
       <c r="M13" t="n">
-        <v>1692000</v>
+        <v>263000</v>
       </c>
       <c r="N13" t="n">
-        <v>49.71</v>
+        <v>46.37</v>
       </c>
       <c r="O13" t="n">
-        <v>3202058537000</v>
+        <v>3341988193250</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R13" t="n">
-        <v>82000</v>
+        <v>78000</v>
       </c>
       <c r="S13" t="n">
-        <v>-70000</v>
+        <v>-934000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>솔리다임 상장 관련 최태원 회장에 대한 비판과 함께, 이재명 정부 정책에 대한 부정적 평가. 외인 자사주 매입 후 매도 및 국장 주가 움직임에 대한 불만 표출.</t>
+          <t>분기 100조 영업이익에도 주가 부양 없는 한국 증시에 대한 불만과 정부 정책 비판이 주를 이루며, 삼성전자의 실적과 주가 괴리에 대한 답답함을 토로함.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['솔리다임', '자사주 매입', '국장']</t>
+          <t>['영업이익', '주가 부양', '한국 증시']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>265250</v>
+        <v>18905</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.21%</t>
+          <t>'-3.25%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>131</v>
       </c>
       <c r="F14" t="n">
-        <v>530</v>
+        <v>74</v>
       </c>
       <c r="G14" t="n">
-        <v>2090</v>
+        <v>361</v>
       </c>
       <c r="H14" t="n">
-        <v>46.38</v>
+        <v>27.68</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>268500</v>
+        <v>19540</v>
       </c>
       <c r="K14" t="n">
-        <v>269500</v>
+        <v>19490</v>
       </c>
       <c r="L14" t="n">
-        <v>270000</v>
+        <v>19500</v>
       </c>
       <c r="M14" t="n">
-        <v>263000</v>
+        <v>18850</v>
       </c>
       <c r="N14" t="n">
-        <v>46.37</v>
+        <v>27.67</v>
       </c>
       <c r="O14" t="n">
-        <v>3265662897500</v>
+        <v>42428646915</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>90200</v>
+        <v>18440</v>
       </c>
       <c r="R14" t="n">
-        <v>78000</v>
+        <v>-451000</v>
       </c>
       <c r="S14" t="n">
-        <v>-934000</v>
+        <v>-69000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>이재명 정부의 레버리지 정책 비판과 함께, 분기 1000조 영업이익에도 불구하고 주가 부양 없는 국장 현실에 대한 강한 불만 표출. 실적과 무관한 주가 흐름에 대한 부정적 전망.</t>
+          <t>조선주 폭락의 주범으로 특정 세력 지목 및 애널리스트들의 추천 종목 손실 발생에 대한 비판. 선박 뉴스 신뢰도 의문 제기 및 페인트 회사 주가 미반영 등 실질적 근거 부족에 따른 부정적 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['레버리지', '영업이익', '주가 부양']</t>
+          <t>['조선주', '폭락', '실적']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18910</v>
+        <v>16710</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.22%</t>
+          <t>'-3.63%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="F15" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>358</v>
+        <v>587</v>
       </c>
       <c r="H15" t="n">
-        <v>27.68</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>19540</v>
+        <v>17340</v>
       </c>
       <c r="K15" t="n">
-        <v>19490</v>
+        <v>17190</v>
       </c>
       <c r="L15" t="n">
-        <v>19500</v>
+        <v>17220</v>
       </c>
       <c r="M15" t="n">
-        <v>18850</v>
+        <v>16660</v>
       </c>
       <c r="N15" t="n">
-        <v>27.67</v>
+        <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>41422300475</v>
+        <v>40490296985</v>
       </c>
       <c r="P15" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>18440</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>-451000</v>
+        <v>-81000</v>
       </c>
       <c r="S15" t="n">
-        <v>-69000</v>
+        <v>-19000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>조선주 폭락의 주범으로 특정 세력 지목 및 애널리스트들의 추천 종목 손실 발생에 대한 비판. 선박 뉴스 신뢰도 의문 제기 및 페인트 회사 주가 미반영 등 실질적 근거 부족에 따른 부정적 전망.</t>
+          <t>AI가 지목한 JP, 한국, 신한, 삼성증권 등 특정 기관 및 증권사에 대한 의혹 제기. 연기금 및 삼성자산운용의 움직임과 공매도에 대한 불만 표출, 주가 조작 및 개인 투자자 손실에 대한 우려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['조선주', '폭락', '실적']</t>
+          <t>['공매도', '주가 조작', '연기금']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16710</v>
+        <v>230000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.63%</t>
+          <t>'-4.56%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.04</v>
+        <v>-0.65</v>
       </c>
       <c r="E16" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="F16" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="G16" t="n">
-        <v>574</v>
+        <v>796</v>
       </c>
       <c r="H16" t="n">
-        <v>9.460000000000001</v>
+        <v>3.47</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17340</v>
+        <v>241000</v>
       </c>
       <c r="K16" t="n">
-        <v>17190</v>
+        <v>227000</v>
       </c>
       <c r="L16" t="n">
-        <v>17220</v>
+        <v>239500</v>
       </c>
       <c r="M16" t="n">
-        <v>16660</v>
+        <v>210500</v>
       </c>
       <c r="N16" t="n">
-        <v>9.5</v>
+        <v>4.12</v>
       </c>
       <c r="O16" t="n">
-        <v>39657508230</v>
+        <v>42631482250</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>1233000</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>120000</v>
       </c>
       <c r="R16" t="n">
-        <v>-81000</v>
+        <v>6000</v>
       </c>
       <c r="S16" t="n">
-        <v>-19000</v>
+        <v>5000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>AI가 지목한 JP, 한국, 신한, 삼성증권 등 특정 기관 및 증권사에 대한 의혹 제기. 연기금 및 삼성자산운용의 움직임과 공매도에 대한 불만 표출, 주가 조작 및 개인 투자자 손실에 대한 우려.</t>
+          <t>삼천당제약의 내년 아일리아 영업이익 전망과 연기금의 7일째 매수, 캐나다 세마 출시 임박 등 긍정적 뉴스가 제시되며, 공매도 금지 조치와 함께 3연상 기대감이 나타남.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공매도', '주가 조작', '연기금']</t>
+          <t>['삼천당제약', '아일리아', '공매도 금지']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,86 +1936,86 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>230000</v>
+        <v>28300</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.56%</t>
+          <t>'-5.03%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.65</v>
+        <v>-0.76</v>
       </c>
       <c r="E17" t="n">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="F17" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="G17" t="n">
-        <v>782</v>
+        <v>183</v>
       </c>
       <c r="H17" t="n">
-        <v>3.47</v>
+        <v>10.02</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>241000</v>
+        <v>29800</v>
       </c>
       <c r="K17" t="n">
-        <v>227000</v>
+        <v>29900</v>
       </c>
       <c r="L17" t="n">
-        <v>239500</v>
+        <v>30000</v>
       </c>
       <c r="M17" t="n">
-        <v>210500</v>
+        <v>28050</v>
       </c>
       <c r="N17" t="n">
-        <v>4.12</v>
+        <v>10.78</v>
       </c>
       <c r="O17" t="n">
-        <v>42167273500</v>
+        <v>61723504100</v>
       </c>
       <c r="P17" t="n">
-        <v>1233000</v>
+        <v>75900</v>
       </c>
       <c r="Q17" t="n">
-        <v>120000</v>
+        <v>15960</v>
       </c>
       <c r="R17" t="n">
-        <v>6000</v>
+        <v>-560000</v>
       </c>
       <c r="S17" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>공매도 과열 예상 속 연기금 7일 연속 매수. 캐나다 세마 출시 기대감 및 릴레이 계약 공시 언급.</t>
+          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['공매도', '계약공시', '수급']</t>
+          <t>['주가 하락', '공매도', '유상증자']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,187 +2023,187 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28350</v>
+        <v>17000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.87%</t>
+          <t>'-5.24%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.76</v>
+        <v>-0.95</v>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="G18" t="n">
-        <v>182</v>
+        <v>538</v>
       </c>
       <c r="H18" t="n">
-        <v>10.02</v>
+        <v>3.97</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>29800</v>
+        <v>17940</v>
       </c>
       <c r="K18" t="n">
-        <v>29900</v>
+        <v>17770</v>
       </c>
       <c r="L18" t="n">
-        <v>30000</v>
+        <v>17940</v>
       </c>
       <c r="M18" t="n">
-        <v>28050</v>
+        <v>16750</v>
       </c>
       <c r="N18" t="n">
-        <v>10.78</v>
+        <v>4.92</v>
       </c>
       <c r="O18" t="n">
-        <v>60947358400</v>
+        <v>94075681840</v>
       </c>
       <c r="P18" t="n">
-        <v>75900</v>
+        <v>31500</v>
       </c>
       <c r="Q18" t="n">
-        <v>15960</v>
+        <v>1272</v>
       </c>
       <c r="R18" t="n">
-        <v>-560000</v>
+        <v>-426000</v>
       </c>
       <c r="S18" t="n">
-        <v>1000</v>
+        <v>-60000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
+          <t>대한광통신의 주가 하락 및 미국 광통신 주식의 동반 하락에 대한 우려가 제기되며, 외인 및 기관의 매도세와 프로그램 매매에 대한 불만이 나타남.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '유상증자']</t>
+          <t>['대한광통신', '주가 하락', '미국 광통신']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16970</v>
+        <v>75700</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.41%</t>
+          <t>'-5.96%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.95</v>
+        <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>128</v>
+        <v>439</v>
       </c>
       <c r="F19" t="n">
-        <v>77</v>
+        <v>260</v>
       </c>
       <c r="G19" t="n">
-        <v>532</v>
+        <v>1273</v>
       </c>
       <c r="H19" t="n">
-        <v>3.97</v>
+        <v>22.49</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>17940</v>
+        <v>80500</v>
       </c>
       <c r="K19" t="n">
-        <v>17770</v>
+        <v>79600</v>
       </c>
       <c r="L19" t="n">
-        <v>17940</v>
+        <v>79600</v>
       </c>
       <c r="M19" t="n">
-        <v>16750</v>
+        <v>75200</v>
       </c>
       <c r="N19" t="n">
-        <v>4.92</v>
+        <v>22.59</v>
       </c>
       <c r="O19" t="n">
-        <v>92704301300</v>
+        <v>204136021450</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>1272</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-426000</v>
+        <v>-579000</v>
       </c>
       <c r="S19" t="n">
-        <v>-60000</v>
+        <v>-91000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 광통신주 하락세 속에서 대한광통신 주가 부진. 외인과 기관의 쌍매도 관찰.</t>
+          <t>두산에너빌리티의 주가 하락에 대한 불만과 공매도 세력에 대한 비판이 제기되며, 원전 관련 내용 및 수출 호조에 대한 언급이 있으나 부정적 심리가 강함.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광통신', '수급', '매도']</t>
+          <t>['두산에너빌리티', '공매도', '하락']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,90 +2212,90 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>75600</v>
+        <v>4855</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.09%</t>
+          <t>'-6.81%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>438</v>
+        <v>92</v>
       </c>
       <c r="F20" t="n">
-        <v>261</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
-        <v>1254</v>
+        <v>329</v>
       </c>
       <c r="H20" t="n">
-        <v>22.49</v>
+        <v>4.65</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>80500</v>
+        <v>5210</v>
       </c>
       <c r="K20" t="n">
-        <v>79600</v>
+        <v>5220</v>
       </c>
       <c r="L20" t="n">
-        <v>79600</v>
+        <v>5310</v>
       </c>
       <c r="M20" t="n">
-        <v>75200</v>
+        <v>4755</v>
       </c>
       <c r="N20" t="n">
-        <v>22.59</v>
+        <v>4.72</v>
       </c>
       <c r="O20" t="n">
-        <v>201137302000</v>
+        <v>68324010267</v>
       </c>
       <c r="P20" t="n">
-        <v>139200</v>
+        <v>8100</v>
       </c>
       <c r="Q20" t="n">
-        <v>57000</v>
+        <v>592</v>
       </c>
       <c r="R20" t="n">
-        <v>-579000</v>
+        <v>-237000</v>
       </c>
       <c r="S20" t="n">
-        <v>-91000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>한미 텍사스 가스발전 확정 소식에 따른 기대감과 함께, 원전 및 건설 관련 정치적 이슈에 대한 우려와 공매도에 대한 불만.</t>
+          <t>전환사채 발행 및 장내 매도에 대한 우려. 광트랜시버 사업 전망에 대한 기대와 함께 급등 가능성에 대한 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['가스발전', '원전', '공매도']</t>
+          <t>['전환사채', '광트랜시버', '장내매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4822</v>
+        <v>15250</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.45%</t>
+          <t>'-8.74%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.44</v>
       </c>
       <c r="E21" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="F21" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="G21" t="n">
-        <v>328</v>
+        <v>194</v>
       </c>
       <c r="H21" t="n">
-        <v>4.65</v>
+        <v>0.93</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,60 +2343,60 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>5210</v>
+        <v>16710</v>
       </c>
       <c r="K21" t="n">
-        <v>5220</v>
+        <v>16460</v>
       </c>
       <c r="L21" t="n">
-        <v>5310</v>
+        <v>17180</v>
       </c>
       <c r="M21" t="n">
-        <v>4755</v>
+        <v>14820</v>
       </c>
       <c r="N21" t="n">
-        <v>4.72</v>
+        <v>2.37</v>
       </c>
       <c r="O21" t="n">
-        <v>67905347683</v>
+        <v>35007787870</v>
       </c>
       <c r="P21" t="n">
-        <v>8100</v>
+        <v>17590</v>
       </c>
       <c r="Q21" t="n">
-        <v>592</v>
+        <v>6320</v>
       </c>
       <c r="R21" t="n">
-        <v>-237000</v>
+        <v>12000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>전환사채 발행 및 장내 매도에 대한 우려. 광트랜시버 사업 전망에 대한 기대와 함께 급등 가능성에 대한 언급.</t>
+          <t>KDB생명 해킹 방어 성공 및 AI 사이버보안 협의체 선정 뉴스. SKT와의 협력 기반 역대 고점 돌파 기대.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['전환사채', '광트랜시버', '장내매도']</t>
+          <t>['양자보안', 'AI', '사이버보안']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7140</v>
+        <v>7130</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.70%</t>
+          <t>'-8.82%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-2.03</v>
       </c>
       <c r="E22" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F22" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G22" t="n">
-        <v>539</v>
+        <v>555</v>
       </c>
       <c r="H22" t="n">
         <v>3.09</v>
@@ -2444,13 +2444,13 @@
         <v>8510</v>
       </c>
       <c r="M22" t="n">
-        <v>7130</v>
+        <v>7120</v>
       </c>
       <c r="N22" t="n">
         <v>5.12</v>
       </c>
       <c r="O22" t="n">
-        <v>84103923020</v>
+        <v>84686944115</v>
       </c>
       <c r="P22" t="n">
         <v>23500</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>본PF 및 대주단 구성에 대한 언급과 함께, 주가 하락에 대한 불만. 부동산 시장과의 연관성 및 과거 유사 주포 운전 방식 언급.</t>
+          <t>삼표시멘트의 수주 및 본PF 관련 내용이 언급되나, 주가 하락과 투매 움직임으로 인해 부정적인 전망이 우세하며, 투자자들의 손실에 대한 불만이 나타남.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['본PF', '대주단', '부동산주']</t>
+          <t>['삼표시멘트', '수주', '주가 하락']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2495,92 +2495,92 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15180</v>
+        <v>52200</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-9.16%</t>
+          <t>'-10.15%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-1.44</v>
+        <v>0.02</v>
       </c>
       <c r="E23" t="n">
-        <v>60</v>
+        <v>330</v>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>159</v>
       </c>
       <c r="G23" t="n">
-        <v>194</v>
+        <v>654</v>
       </c>
       <c r="H23" t="n">
-        <v>0.93</v>
+        <v>1.32</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>16710</v>
+        <v>58100</v>
       </c>
       <c r="K23" t="n">
-        <v>16460</v>
+        <v>63200</v>
       </c>
       <c r="L23" t="n">
-        <v>17180</v>
+        <v>63800</v>
       </c>
       <c r="M23" t="n">
-        <v>14820</v>
+        <v>51700</v>
       </c>
       <c r="N23" t="n">
-        <v>2.37</v>
+        <v>1.3</v>
       </c>
       <c r="O23" t="n">
-        <v>34456022490</v>
+        <v>56024991600</v>
       </c>
       <c r="P23" t="n">
-        <v>17590</v>
+        <v>63800</v>
       </c>
       <c r="Q23" t="n">
-        <v>6320</v>
+        <v>25600</v>
       </c>
       <c r="R23" t="n">
-        <v>12000</v>
+        <v>-173000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>KDB생명 해킹 방어 성공 및 AI 사이버보안 협의체 선정 뉴스. SKT와의 협력 기반 역대 고점 돌파 기대.</t>
+          <t>에페 식약처 승인에도 불구하고 이해할 수 없는 급락과 주가 조작 의혹 제기. 공매도 및 기관 매도 의심.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['양자보안', 'AI', '사이버보안']</t>
+          <t>['주가 조작', '공매도', '기술 수출']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9830</v>
+        <v>9810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.72%</t>
+          <t>'-10.90%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F24" t="n">
         <v>64</v>
       </c>
       <c r="G24" t="n">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="H24" t="n">
         <v>5.04</v>
@@ -2634,7 +2634,7 @@
         <v>5.01</v>
       </c>
       <c r="O24" t="n">
-        <v>7134112810</v>
+        <v>7183769965</v>
       </c>
       <c r="P24" t="n">
         <v>15900</v>
